--- a/data/compounder_radar.xlsx
+++ b/data/compounder_radar.xlsx
@@ -426,16 +426,16 @@
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="23" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="23" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
     <col width="8" customWidth="1" min="14" max="14"/>
     <col width="45" customWidth="1" min="15" max="15"/>
     <col width="19" customWidth="1" min="16" max="16"/>
     <col width="18" customWidth="1" min="17" max="17"/>
-    <col width="21" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
     <col width="21" customWidth="1" min="19" max="19"/>
     <col width="21" customWidth="1" min="20" max="20"/>
   </cols>
@@ -545,19 +545,19 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Micron Technology, Inc.</t>
+          <t>Arista Networks, Inc.</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>81.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -565,27 +565,29 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.06713489726936261</v>
+        <v>0.2714652572159764</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.006929629272242499</v>
+        <v>0.3708447402164197</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7256899999999999</v>
+        <v>0.63004</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3487</v>
+        <v>0.14119</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8351558770343581</v>
+        <v>0.2648009752477871</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.8728631705846895</v>
+        <v>-0.3930142576986272</v>
       </c>
       <c r="L2" t="n">
-        <v>0.9568004530136458</v>
-      </c>
-      <c r="M2" t="inlineStr"/>
+        <v>0.6737693863789616</v>
+      </c>
+      <c r="M2" t="n">
+        <v>237955268608</v>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>High</t>
@@ -593,43 +595,43 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Høj bruttomargin, positivt momentum, analytiker-upside over 20 %</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="Q2" t="b">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>0.5916866288645946</v>
+        <v>0.3310052780877977</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8896770801335447</v>
+        <v>0.4663091696109241</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-08-04 06:39:46</t>
+          <t>2026-08-09 07:56:42</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices, Inc.</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>79.90000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="D3" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -637,30 +639,32 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.1364359933536843</v>
+        <v>1.000450949944396</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4666355102918431</v>
+        <v>2.04239508347386</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5306</v>
+        <v>0.74144995</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03647</v>
+        <v>0.52727</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1949207659293497</v>
+        <v>0.3521502946954813</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.6921013535820403</v>
+        <v>-0.2674138238971245</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2816361576530917</v>
-      </c>
-      <c r="M3" t="inlineStr"/>
+        <v>1.316873935548505</v>
+      </c>
+      <c r="M3" t="n">
+        <v>5424535306240</v>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -669,39 +673,39 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="Q3" t="b">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3431972891016541</v>
+        <v>0.06014672155350387</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8881354894345377</v>
+        <v>0.3045914419713429</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-08-04 06:39:46</t>
+          <t>2026-08-09 07:56:42</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Eli Lilly and Company</t>
+          <t>Micron Technology, Inc.</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>76.90000000000001</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -709,27 +713,29 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.3168737488062043</v>
+        <v>0.06713489726936261</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5171329563234539</v>
+        <v>-0.006929629272242499</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8283199999999999</v>
+        <v>0.7256899999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.20739001</v>
+        <v>0.3487</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1387614147107084</v>
+        <v>0.7115178276376812</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.4437290433045588</v>
+        <v>-0.8707111683398475</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3127165480927688</v>
-      </c>
-      <c r="M4" t="inlineStr"/>
+        <v>0.8171686013793824</v>
+      </c>
+      <c r="M4" t="n">
+        <v>991121571840</v>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>High</t>
@@ -737,43 +743,43 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
+          <t>Høj bruttomargin, positivt momentum, analytiker-upside over 20 %</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="Q4" t="b">
         <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2313477828196622</v>
+        <v>0.3573526703199177</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1255671610267297</v>
+        <v>1.293279161436129</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-08-04 06:39:46</t>
+          <t>2026-08-09 07:56:42</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Fortinet, Inc.</t>
+          <t>Advanced Micro Devices, Inc.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FTNT</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>76.8</v>
+        <v>76</v>
       </c>
       <c r="D5" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -781,28 +787,28 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.1546194776009138</v>
+        <v>0.1364359933536843</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3167495145145989</v>
+        <v>0.4666355102918431</v>
       </c>
       <c r="H5" t="n">
-        <v>0.80204004</v>
+        <v>0.55724</v>
       </c>
       <c r="I5" t="n">
-        <v>0.14166</v>
+        <v>0.05128</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.02264873475889961</v>
+        <v>0.2688985435286328</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.5703694626554745</v>
+        <v>-0.6912859980139027</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.03970888387581917</v>
+        <v>0.3889830609923983</v>
       </c>
       <c r="M5" t="n">
-        <v>119749410816</v>
+        <v>789073100800</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -821,60 +827,62 @@
         <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9208872214198582</v>
+        <v>0.1833716776756134</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9868726868338145</v>
+        <v>1.51096096286526</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-08-04 06:39:46</t>
+          <t>2026-08-09 07:56:42</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sandisk Corporation</t>
+          <t>Fortinet, Inc.</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>FTNT</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>74.5</v>
+        <v>75.5</v>
       </c>
       <c r="D6" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>High Conviction</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.09932312697218015</v>
-      </c>
-      <c r="G6" t="inlineStr"/>
+        <v>0.1546194776009138</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.3167495145145989</v>
+      </c>
       <c r="H6" t="n">
-        <v>0.56038</v>
+        <v>0.80204004</v>
       </c>
       <c r="I6" t="n">
-        <v>0.22823</v>
+        <v>0.14166</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7218331094772636</v>
+        <v>0.007672575795540038</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.9685333416147139</v>
+        <v>-0.5392758707090954</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7452847294589178</v>
+        <v>0.01422755256127322</v>
       </c>
       <c r="M6" t="n">
-        <v>190744051712</v>
+        <v>117130051584</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -883,43 +891,43 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Høj bruttomargin, positivt momentum, analytiker-upside over 20 %</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="Q6" t="b">
         <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1079059427048485</v>
+        <v>0.4785588365728168</v>
       </c>
       <c r="S6" t="n">
-        <v>1.252605198502335</v>
+        <v>1.022551612471996</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-08-04 06:39:46</t>
+          <t>2026-08-09 07:56:42</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc.</t>
+          <t>Amphenol Corporation</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>APH</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>70.7</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -927,28 +935,28 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.03534983888485344</v>
+        <v>0.2230660589034148</v>
       </c>
       <c r="G7" t="n">
-        <v>0.388859258627138</v>
+        <v>0.2972340671812952</v>
       </c>
       <c r="H7" t="n">
-        <v>0.19212</v>
+        <v>0.38952</v>
       </c>
       <c r="I7" t="n">
-        <v>0.07004000000000001</v>
+        <v>0.14473</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1719328236445854</v>
+        <v>0.1706987823619812</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.743088900284369</v>
+        <v>-0.3810734129329708</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2313758469259725</v>
+        <v>0.4479419885217928</v>
       </c>
       <c r="M7" t="n">
-        <v>277208006656</v>
+        <v>208596123648</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -957,7 +965,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Stærk eps-vækst, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, positivt momentum</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -967,33 +975,33 @@
         <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9432393281153402</v>
+        <v>0.2401934174574814</v>
       </c>
       <c r="S7" t="n">
-        <v>2.437388951944431</v>
+        <v>0.3301740732320491</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-08-04 06:39:46</t>
+          <t>2026-08-09 07:56:42</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Marvell Technology, Inc.</t>
+          <t>Broadcom Inc.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>70.5</v>
+        <v>74.8</v>
       </c>
       <c r="D8" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1001,71 +1009,73 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.1144958764235571</v>
-      </c>
-      <c r="G8" t="inlineStr"/>
+        <v>0.2437842600004176</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.2159817111378917</v>
+      </c>
       <c r="H8" t="n">
-        <v>0.5150299699999999</v>
+        <v>0.76284</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03808</v>
+        <v>0.121190004</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3258376983615017</v>
+        <v>0.2340669066766412</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6829312346793962</v>
+        <v>-0.3410557321862726</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4771164091132353</v>
+        <v>0.686301048735349</v>
       </c>
       <c r="M8" t="n">
-        <v>173921665024</v>
+        <v>2035102646272</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="Q8" t="b">
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1359749795783063</v>
+        <v>0.03848414109854015</v>
       </c>
       <c r="S8" t="n">
-        <v>1.307600188596483</v>
+        <v>0.3826792124922158</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-08-04 06:39:46</t>
+          <t>2026-08-09 07:56:42</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Howmet Aerospace Inc.</t>
+          <t>Palantir Technologies Inc.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HWM</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>70.40000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="D9" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1073,28 +1083,26 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.1337158522423005</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.495146138791156</v>
-      </c>
+        <v>0.3291712528765784</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>0.35046002</v>
+        <v>0.84796</v>
       </c>
       <c r="I9" t="n">
-        <v>0.11918</v>
+        <v>0.17292999</v>
       </c>
       <c r="J9" t="n">
-        <v>0.09285464832017887</v>
+        <v>0.1040184872972503</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.408220996018719</v>
+        <v>-0.3816057205976396</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2274617161433828</v>
+        <v>0.2725810481413775</v>
       </c>
       <c r="M9" t="n">
-        <v>114566774784</v>
+        <v>413350068224</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -1103,43 +1111,43 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, positivt momentum</t>
+          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="Q9" t="b">
         <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1618842604945363</v>
+        <v>0.2550893154075689</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3523480848477396</v>
+        <v>0.3230520865670188</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-08-04 06:39:46</t>
+          <t>2026-08-09 07:56:42</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Interactive Brokers Group, Inc.</t>
+          <t>Booking Holdings Inc. Common St</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IBKR</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>69.40000000000001</v>
+        <v>74</v>
       </c>
       <c r="D10" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1147,28 +1155,28 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.3459787421885367</v>
+        <v>0.1634869878187224</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3328887406583814</v>
+        <v>0.2943673092572356</v>
       </c>
       <c r="H10" t="n">
-        <v>0.93036</v>
+        <v>0.87227994</v>
       </c>
       <c r="I10" t="n">
-        <v>0.022839999</v>
+        <v>0.2038</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2189933903133903</v>
+        <v>0.1069914653483817</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.3282051282051281</v>
+        <v>-0.2997854677735287</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6672454861111111</v>
+        <v>0.3568934349719974</v>
       </c>
       <c r="M10" t="n">
-        <v>148843495424</v>
+        <v>166149439488</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1187,33 +1195,33 @@
         <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1079134997425473</v>
+        <v>0.2550153802075548</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1653941636847271</v>
+        <v>0.2121822677669754</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-08-04 06:39:46</t>
+          <t>2026-08-09 07:56:42</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>F5, Inc.</t>
+          <t>ServiceNow, Inc.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>NOW</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>69.3</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1221,37 +1229,37 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.04631913174341684</v>
+        <v>0.2237651786474262</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3082491584064506</v>
+        <v>0.7345580184539504</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8192700000000001</v>
+        <v>0.74768996</v>
       </c>
       <c r="I11" t="n">
-        <v>0.07995999600000001</v>
+        <v>0.04249</v>
       </c>
       <c r="J11" t="n">
-        <v>0.07321274763135222</v>
+        <v>0.1231007367072392</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.4493417005044913</v>
+        <v>-0.3494554772581678</v>
       </c>
       <c r="L11" t="n">
-        <v>0.162933347938003</v>
+        <v>0.352264436296976</v>
       </c>
       <c r="M11" t="n">
-        <v>23091245056</v>
+        <v>129108688896</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -1261,33 +1269,33 @@
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2428836520845277</v>
+        <v>0.3343306137395301</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4248752665683944</v>
+        <v>0.2167982129538544</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-08-04 06:39:46</t>
+          <t>2026-08-09 07:56:42</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Applied Materials, Inc.</t>
+          <t>DexCom, Inc.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>DXCM</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>68.8</v>
+        <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1295,28 +1303,28 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.03233470456886756</v>
+        <v>0.1701360960301399</v>
       </c>
       <c r="G12" t="n">
-        <v>0.05191743203490939</v>
+        <v>0.365979383233586</v>
       </c>
       <c r="H12" t="n">
-        <v>0.48956</v>
+        <v>0.62473</v>
       </c>
       <c r="I12" t="n">
-        <v>0.14858</v>
+        <v>0.103310004</v>
       </c>
       <c r="J12" t="n">
-        <v>0.211202350398487</v>
+        <v>0.1025368731563421</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.7019162115744583</v>
+        <v>-0.3615339233038348</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3008939627206245</v>
+        <v>0.2836161879895558</v>
       </c>
       <c r="M12" t="n">
-        <v>411437727744</v>
+        <v>31981324288</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1325,7 +1333,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Høj bruttomargin, positivt momentum, analytiker-upside over 20 %</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -1335,33 +1343,33 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0.288501973340042</v>
+        <v>0.3913971468118593</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4909915340075093</v>
+        <v>0.2126198417531036</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-08-04 06:39:46</t>
+          <t>2026-08-09 07:56:42</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>United Airlines Holdings, Inc.</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>UAL</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>68.8</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1369,28 +1377,28 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.09529134601036815</v>
+        <v>0.1612397915820203</v>
       </c>
       <c r="G13" t="n">
-        <v>0.6599631084110487</v>
+        <v>0.2285599828574523</v>
       </c>
       <c r="H13" t="n">
-        <v>0.31816</v>
+        <v>0.67944</v>
       </c>
       <c r="I13" t="n">
-        <v>0.03381</v>
+        <v>0.14088</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2629658073058649</v>
+        <v>0.1267206544130883</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.3407586260612196</v>
+        <v>-0.3015860317206345</v>
       </c>
       <c r="L13" t="n">
-        <v>0.7717069714285716</v>
+        <v>0.4201807812189138</v>
       </c>
       <c r="M13" t="n">
-        <v>41671507968</v>
+        <v>3712698548224</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1399,7 +1407,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Stærk eps-vækst, positivt momentum, analytiker-upside over 20 %</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -1409,33 +1417,33 @@
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0.3481111314561631</v>
+        <v>0.1908475313223374</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1673080525416732</v>
+        <v>0.2757298821491341</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-08-04 06:39:46</t>
+          <t>2026-08-09 07:56:42</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DexCom, Inc.</t>
+          <t>Datadog, Inc.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DXCM</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>68.7</v>
+        <v>71.2</v>
       </c>
       <c r="D14" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1443,28 +1451,26 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.1701360960301399</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.365979383233586</v>
-      </c>
+        <v>0.2694953937625746</v>
+      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0.62473</v>
+        <v>0.79536</v>
       </c>
       <c r="I14" t="n">
-        <v>0.103310004</v>
+        <v>0.0018000001</v>
       </c>
       <c r="J14" t="n">
-        <v>0.06287939525827513</v>
+        <v>0.1946964476552815</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.3802542664070554</v>
+        <v>-0.5810285128029753</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1653614457831325</v>
+        <v>0.3350893172454384</v>
       </c>
       <c r="M14" t="n">
-        <v>32947367936</v>
+        <v>83998416896</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1473,43 +1479,43 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
+          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="Q14" t="b">
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0.4013433756067564</v>
+        <v>0.2394955649418622</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1277026614627323</v>
+        <v>1.191792235717045</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-08-04 06:39:46</t>
+          <t>2026-08-09 07:56:42</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Eli Lilly and Company</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>68.7</v>
+        <v>71</v>
       </c>
       <c r="D15" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1517,37 +1523,37 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0.1631543559703441</v>
+        <v>0.3168737488062043</v>
       </c>
       <c r="G15" t="n">
-        <v>4.460320482827598</v>
+        <v>0.5171329563234539</v>
       </c>
       <c r="H15" t="n">
-        <v>0.31051</v>
+        <v>0.83399004</v>
       </c>
       <c r="I15" t="n">
-        <v>0.05065</v>
+        <v>0.20357001</v>
       </c>
       <c r="J15" t="n">
-        <v>0.09751104545577749</v>
+        <v>0.0900853497060834</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.2849592063535088</v>
+        <v>-0.4721306221588754</v>
       </c>
       <c r="L15" t="n">
-        <v>0.3421929991439169</v>
+        <v>0.1908059877458426</v>
       </c>
       <c r="M15" t="n">
-        <v>382787911680</v>
+        <v>1056890945536</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -1557,33 +1563,33 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0.2434686346707913</v>
+        <v>0.2182561529182798</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2080707511550817</v>
+        <v>0.1654455488311153</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-08-04 06:39:46</t>
+          <t>2026-08-09 07:56:42</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Incyte Corporation</t>
+          <t>Seagate Technology Holdings PLC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>INCY</t>
+          <t>STX</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>68.59999999999999</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1591,28 +1597,26 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0.1483959547833886</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.6156160063417289</v>
-      </c>
+        <v>0.1820341908356484</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>0.55659</v>
+        <v>0.45576</v>
       </c>
       <c r="I16" t="n">
-        <v>0.16832</v>
+        <v>0.29354998</v>
       </c>
       <c r="J16" t="n">
-        <v>0.03822105885333094</v>
+        <v>0.3729386288695309</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.3626614877986997</v>
+        <v>-0.8139303115310793</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1053904540162976</v>
+        <v>0.4581947908636039</v>
       </c>
       <c r="M16" t="n">
-        <v>24005494784</v>
+        <v>184496521216</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1621,43 +1625,43 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
+          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="Q16" t="b">
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0.254539738159683</v>
+        <v>0.06119135769116801</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1824297039767804</v>
+        <v>1.009516040690849</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-08-04 06:39:46</t>
+          <t>2026-08-09 07:56:42</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise Comp</t>
+          <t>Interactive Brokers Group, Inc.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HPE</t>
+          <t>IBKR</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>68.5</v>
+        <v>69.5</v>
       </c>
       <c r="D17" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1665,71 +1669,73 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0.06370170685761956</v>
-      </c>
-      <c r="G17" t="inlineStr"/>
+        <v>0.3459787421885367</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.3328887406583814</v>
+      </c>
       <c r="H17" t="n">
-        <v>0.33776</v>
+        <v>0.93036</v>
       </c>
       <c r="I17" t="n">
-        <v>0.01966</v>
+        <v>0.022839999</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3048839570063695</v>
+        <v>0.2083949675509507</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.6091759554140127</v>
+        <v>-0.3288170329044745</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5004858683221697</v>
+        <v>0.6337718144044321</v>
       </c>
       <c r="M17" t="n">
-        <v>66527985664</v>
+        <v>149646131200</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Positivt momentum, analytiker-upside over 20 %</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="Q17" t="b">
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6697998718596914</v>
+        <v>0.05028029086934649</v>
       </c>
       <c r="S17" t="n">
-        <v>1.196724689910953</v>
+        <v>0.2665621031697569</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-08-04 06:39:46</t>
+          <t>2026-08-09 07:56:42</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Delta Air Lines, Inc.</t>
+          <t>Marvell Technology, Inc.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>68.09999999999999</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1737,27 +1743,27 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0.07799197884220499</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.5492464741024845</v>
-      </c>
+        <v>0.1144958764235571</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>0.187</v>
+        <v>0.5150299699999999</v>
       </c>
       <c r="I18" t="n">
-        <v>0.04019</v>
+        <v>0.03808</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1520999017359974</v>
+        <v>0.1746260058522311</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.4406594606398079</v>
+        <v>-0.7190929041697147</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3451642715559961</v>
-      </c>
-      <c r="M18" t="inlineStr"/>
+        <v>0.2428420651068158</v>
+      </c>
+      <c r="M18" t="n">
+        <v>196310925312</v>
+      </c>
       <c r="N18" t="inlineStr">
         <is>
           <t>High</t>
@@ -1765,7 +1771,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Stærk eps-vækst, positivt momentum</t>
+          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -1775,33 +1781,33 @@
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>0.292667485740369</v>
+        <v>0.3672517932141015</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3244253549655423</v>
+        <v>1.94951442905662</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-08-04 06:39:46</t>
+          <t>2026-08-09 07:56:42</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Seagate Technology Holdings PLC</t>
+          <t>Axon Enterprise, Inc.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>STX</t>
+          <t>AXON</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>66.7</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1809,26 +1815,28 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>-0.07943569063297951</v>
-      </c>
-      <c r="G19" t="inlineStr"/>
+        <v>0.3278726393918761</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-0.09393302099393697</v>
+      </c>
       <c r="H19" t="n">
-        <v>0.45576</v>
+        <v>0.5952499999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>0.29354998</v>
+        <v>0.00509</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3309350708733425</v>
+        <v>0.2115816885868897</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.8258248501913219</v>
+        <v>-0.4062976130015237</v>
       </c>
       <c r="L19" t="n">
-        <v>0.400732759248736</v>
+        <v>0.5207554310344823</v>
       </c>
       <c r="M19" t="n">
-        <v>188650618880</v>
+        <v>46387376128</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1837,43 +1845,43 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Høj bruttomargin, positivt momentum, analytiker-upside over 20 %</t>
+          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="Q19" t="b">
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2718075367116708</v>
+        <v>0.3376045121033731</v>
       </c>
       <c r="S19" t="n">
-        <v>0.9218372800974317</v>
+        <v>0.4287752245369121</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-08-04 06:39:46</t>
+          <t>2026-08-09 07:56:42</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>United Rentals, Inc.</t>
+          <t>KLA Corporation</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>URI</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>66.2</v>
+        <v>67.8</v>
       </c>
       <c r="D20" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1881,28 +1889,28 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0.1140989591195885</v>
+        <v>0.09685534331651668</v>
       </c>
       <c r="G20" t="n">
-        <v>0.09200602525921697</v>
+        <v>0.1148114331133121</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3848</v>
+        <v>0.6130100000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>0.08767999999999999</v>
+        <v>0.20799999</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1308004158004159</v>
+        <v>0.1652710615314723</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.3712900566348842</v>
+        <v>-0.5799101509262531</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3522863418048418</v>
+        <v>0.2849942551746947</v>
       </c>
       <c r="M20" t="n">
-        <v>69457641472</v>
+        <v>258839986176</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -1911,7 +1919,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, positivt momentum</t>
+          <t>Høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P20" t="n">
@@ -1921,33 +1929,33 @@
         <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1267389487628878</v>
+        <v>0.1249843058235034</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3772174384961748</v>
+        <v>0.4922324438519448</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-08-04 06:39:46</t>
+          <t>2026-08-09 07:56:42</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Datadog, Inc.</t>
+          <t>Veeva Systems Inc.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>64.59999999999999</v>
+        <v>66.3</v>
       </c>
       <c r="D21" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1955,26 +1963,28 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0.2694953937625746</v>
-      </c>
-      <c r="G21" t="inlineStr"/>
+        <v>0.1402968452680178</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.2194365698361114</v>
+      </c>
       <c r="H21" t="n">
-        <v>0.79906</v>
+        <v>0.75021005</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.0021600001</v>
+        <v>0.07298</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.01328581871345047</v>
+        <v>0.05932594263895519</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6417763157894737</v>
+        <v>-0.3576170434329847</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.02070163448943589</v>
+        <v>0.1658923804901723</v>
       </c>
       <c r="M21" t="n">
-        <v>97390706688</v>
+        <v>37438308352</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -1983,43 +1993,43 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="Q21" t="b">
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>1.02715785060585</v>
+        <v>0.3698068423221583</v>
       </c>
       <c r="S21" t="n">
-        <v>1.090575881826636</v>
+        <v>0.2535762500379706</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-08-04 06:39:46</t>
+          <t>2026-08-09 07:56:42</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Cisco Systems, Inc.</t>
+          <t>United Airlines Holdings, Inc.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>UAL</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>64.09999999999999</v>
+        <v>65.5</v>
       </c>
       <c r="D22" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -2027,37 +2037,37 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0.03192384157728467</v>
+        <v>0.09529134601036815</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.0254656916401832</v>
+        <v>0.6599631084110487</v>
       </c>
       <c r="H22" t="n">
-        <v>0.64296997</v>
+        <v>0.31816</v>
       </c>
       <c r="I22" t="n">
-        <v>0.07337</v>
+        <v>0.03381</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1240053512860348</v>
+        <v>0.2515605125038591</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.4325047471085793</v>
+        <v>-0.3467119481321396</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2867144282578327</v>
+        <v>0.7255605520926088</v>
       </c>
       <c r="M22" t="n">
-        <v>456654618624</v>
+        <v>42051252224</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Høj bruttomargin, positivt momentum</t>
+          <t>Stærk eps-vækst, positivt momentum, analytiker-upside over 20 %</t>
         </is>
       </c>
       <c r="P22" t="n">
@@ -2067,33 +2077,33 @@
         <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>0.2723924311141501</v>
+        <v>0.2994985107758124</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4924743780154592</v>
+        <v>0.2212272790165106</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-08-04 06:39:46</t>
+          <t>2026-08-09 07:56:42</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Palo Alto Networks, Inc.</t>
+          <t>Applied Materials, Inc.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>63.4</v>
+        <v>65.3</v>
       </c>
       <c r="D23" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -2101,26 +2111,28 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0.1878825003317091</v>
-      </c>
-      <c r="G23" t="inlineStr"/>
+        <v>0.03233470456886756</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.05191743203490939</v>
+      </c>
       <c r="H23" t="n">
-        <v>0.71963996</v>
+        <v>0.48956</v>
       </c>
       <c r="I23" t="n">
-        <v>0.017719999</v>
+        <v>0.14858</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.03004407570650758</v>
+        <v>0.1667787587639575</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.5979316106357848</v>
+        <v>-0.7134881477909263</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.05024667566004999</v>
+        <v>0.2337512673200407</v>
       </c>
       <c r="M23" t="n">
-        <v>282910949376</v>
+        <v>428055298048</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -2129,43 +2141,43 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
+          <t>Høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="Q23" t="b">
         <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>0.8504905923425592</v>
+        <v>0.3145583294175336</v>
       </c>
       <c r="S23" t="n">
-        <v>0.8832576181584095</v>
+        <v>0.7779648791718274</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-08-04 06:39:46</t>
+          <t>2026-08-09 07:56:42</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Garmin Ltd.</t>
+          <t>Dell Technologies Inc.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GRMN</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>63.1</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D24" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -2173,28 +2185,28 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0.142358869424539</v>
+        <v>0.03534983888485344</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1945038186480894</v>
+        <v>0.388859258627138</v>
       </c>
       <c r="H24" t="n">
-        <v>0.60081</v>
+        <v>0.19212</v>
       </c>
       <c r="I24" t="n">
-        <v>0.12174</v>
+        <v>0.07004000000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.06858790523690772</v>
+        <v>0.108012032527492</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.3874852342827143</v>
+        <v>-0.757101615355797</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.1770077906681344</v>
+        <v>0.1426651724639792</v>
       </c>
       <c r="M24" t="n">
-        <v>58773741568</v>
+        <v>293200035840</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -2203,7 +2215,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
+          <t>Stærk eps-vækst, positivt momentum</t>
         </is>
       </c>
       <c r="P24" t="n">
@@ -2213,33 +2225,33 @@
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0.1749672436383698</v>
+        <v>0.9738559714176462</v>
       </c>
       <c r="S24" t="n">
-        <v>0.4474088350041829</v>
+        <v>2.951175825528565</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-08-04 06:39:46</t>
+          <t>2026-08-09 07:56:42</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Monster Beverage Corporation</t>
+          <t>Howmet Aerospace Inc.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MNST</t>
+          <t>HWM</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>63.1</v>
+        <v>64.3</v>
       </c>
       <c r="D25" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -2247,28 +2259,28 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0.09536818669323455</v>
+        <v>0.1337158522423005</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2027507069649817</v>
+        <v>0.495146138791156</v>
       </c>
       <c r="H25" t="n">
-        <v>0.55471003</v>
+        <v>0.36032</v>
       </c>
       <c r="I25" t="n">
-        <v>0.17725</v>
+        <v>0.12815</v>
       </c>
       <c r="J25" t="n">
-        <v>0.03037199358631759</v>
+        <v>0.1363984674329501</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.3742383752004276</v>
+        <v>-0.3988576699304669</v>
       </c>
       <c r="L25" t="n">
-        <v>0.08115681233933193</v>
+        <v>0.3419727830650181</v>
       </c>
       <c r="M25" t="n">
-        <v>91492663296</v>
+        <v>112414146560</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -2277,7 +2289,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, positivt momentum</t>
         </is>
       </c>
       <c r="P25" t="n">
@@ -2287,33 +2299,33 @@
         <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0.2505514160510702</v>
+        <v>0.0352259372142707</v>
       </c>
       <c r="S25" t="n">
-        <v>0.2041478779483716</v>
+        <v>0.3466684453814286</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-08-04 06:39:46</t>
+          <t>2026-08-09 07:56:42</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Garmin Ltd.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>GRMN</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>63.1</v>
+        <v>64</v>
       </c>
       <c r="D26" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -2321,71 +2333,73 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0.09524171431647233</v>
+        <v>0.142358869424539</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1840868065525754</v>
+        <v>0.1945038186480894</v>
       </c>
       <c r="H26" t="n">
-        <v>0.87641</v>
-      </c>
-      <c r="I26" t="inlineStr"/>
+        <v>0.60081</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.12174</v>
+      </c>
       <c r="J26" t="n">
-        <v>0.119069024286323</v>
+        <v>-0.06627520988130842</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.34000852151683</v>
+        <v>-0.3995625462382193</v>
       </c>
       <c r="L26" t="n">
-        <v>0.3501942355889726</v>
+        <v>-0.165869425213331</v>
       </c>
       <c r="M26" t="n">
-        <v>332053544960</v>
+        <v>59957067776</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="Q26" t="b">
         <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>0.1101228654517645</v>
+        <v>0.2908933123836939</v>
       </c>
       <c r="S26" t="n">
-        <v>0.1726314606153021</v>
+        <v>0.5776529045416638</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-08-04 06:39:46</t>
+          <t>2026-08-09 07:56:42</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Arista Networks, Inc.</t>
+          <t>Hewlett Packard Enterprise Comp</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>HPE</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>62.4</v>
+        <v>63.8</v>
       </c>
       <c r="D27" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -2393,28 +2407,26 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>0.2714652572159764</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.3708447402164197</v>
-      </c>
+        <v>0.06370170685761956</v>
+      </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>0.63537</v>
+        <v>0.33776</v>
       </c>
       <c r="I27" t="n">
-        <v>0.14359</v>
+        <v>0.01966</v>
       </c>
       <c r="J27" t="n">
-        <v>0.04013375520579809</v>
+        <v>0.2318183013904549</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.3806046838660825</v>
+        <v>-0.6272078166102969</v>
       </c>
       <c r="L27" t="n">
-        <v>0.1054473497228934</v>
+        <v>0.3696036548831638</v>
       </c>
       <c r="M27" t="n">
-        <v>232807825408</v>
+        <v>70474113024</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2423,43 +2435,43 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
+          <t>Positivt momentum, analytiker-upside over 20 %</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="Q27" t="b">
         <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>0.04423599729404093</v>
+        <v>0.7971617803249145</v>
       </c>
       <c r="S27" t="n">
-        <v>0.2173473745097154</v>
+        <v>1.365472550960148</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-08-04 06:39:46</t>
+          <t>2026-08-09 07:56:42</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Western Digital Corporation</t>
+          <t>F5, Inc.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>61.4</v>
+        <v>63.3</v>
       </c>
       <c r="D28" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -2467,27 +2479,29 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>-0.2028373451127182</v>
+        <v>0.04631913174341684</v>
       </c>
       <c r="G28" t="n">
-        <v>0.02660358695900467</v>
+        <v>0.3082491584064506</v>
       </c>
       <c r="H28" t="n">
-        <v>0.45428002</v>
+        <v>0.81865996</v>
       </c>
       <c r="I28" t="n">
-        <v>0.14648</v>
+        <v>0.07976999999999999</v>
       </c>
       <c r="J28" t="n">
-        <v>0.2433139865710707</v>
+        <v>0.08962346650675856</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.8612723341299647</v>
+        <v>-0.4409214701546611</v>
       </c>
       <c r="L28" t="n">
-        <v>0.2825052854122619</v>
-      </c>
-      <c r="M28" t="inlineStr"/>
+        <v>0.2032640108800362</v>
+      </c>
+      <c r="M28" t="n">
+        <v>22663899136</v>
+      </c>
       <c r="N28" t="inlineStr">
         <is>
           <t>High</t>
@@ -2495,43 +2509,43 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Høj bruttomargin, positivt momentum, analytiker-upside over 20 %</t>
+          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="Q28" t="b">
         <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>0.2542163342381683</v>
+        <v>0.1600197777829866</v>
       </c>
       <c r="S28" t="n">
-        <v>0.958417094494876</v>
+        <v>0.4757200088353686</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-08-04 06:39:46</t>
+          <t>2026-08-09 07:56:42</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CrowdStrike Holdings, Inc.</t>
+          <t>Expedia Group, Inc.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>EXPE</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>61</v>
+        <v>63.3</v>
       </c>
       <c r="D29" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -2539,26 +2553,28 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>0.2900686653697968</v>
-      </c>
-      <c r="G29" t="inlineStr"/>
+        <v>0.08087962506974211</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.6534957812135467</v>
+      </c>
       <c r="H29" t="n">
-        <v>0.75136</v>
+        <v>0.90433</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0100300005</v>
+        <v>0.061079998</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.0464619334452453</v>
+        <v>0.02383713145358568</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.5769724498864421</v>
+        <v>-0.4034376207029742</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.08052712647612513</v>
+        <v>0.05908504866762405</v>
       </c>
       <c r="M29" t="n">
-        <v>206238220288</v>
+        <v>37287608320</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2567,24 +2583,24 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="Q29" t="b">
         <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>0.7127089230317583</v>
+        <v>0.2316136480683892</v>
       </c>
       <c r="S29" t="n">
-        <v>0.717061784952312</v>
+        <v>0.3489626342686869</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2026-08-04 06:39:46</t>
+          <t>2026-08-09 07:56:42</t>
         </is>
       </c>
     </row>
@@ -2600,10 +2616,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>60.5</v>
+        <v>62.5</v>
       </c>
       <c r="D30" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -2617,22 +2633,22 @@
         <v>-0.09938459624739093</v>
       </c>
       <c r="H30" t="n">
-        <v>0.7846</v>
+        <v>0.7800700699999999</v>
       </c>
       <c r="I30" t="n">
-        <v>0.086660005</v>
+        <v>0.084910005</v>
       </c>
       <c r="J30" t="n">
-        <v>0.05456159034433794</v>
+        <v>0.05611930065135406</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.3688320908768193</v>
+        <v>-0.3904696606102159</v>
       </c>
       <c r="L30" t="n">
-        <v>0.1479307025986525</v>
+        <v>0.1437225636523264</v>
       </c>
       <c r="M30" t="n">
-        <v>16861916160</v>
+        <v>17460494336</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2651,33 +2667,33 @@
         <v>1</v>
       </c>
       <c r="R30" t="n">
-        <v>0.430643108686364</v>
+        <v>0.4525172025700568</v>
       </c>
       <c r="S30" t="n">
-        <v>0.1608523114354838</v>
+        <v>0.3144366553078433</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2026-08-04 06:39:46</t>
+          <t>2026-08-09 07:56:42</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lam Research Corporation</t>
+          <t>Corpay, Inc.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>60</v>
+        <v>62.3</v>
       </c>
       <c r="D31" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -2685,28 +2701,28 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>0.02285830538778799</v>
+        <v>0.097332408585459</v>
       </c>
       <c r="G31" t="n">
-        <v>0.08212873820510125</v>
+        <v>0.06564477917470324</v>
       </c>
       <c r="H31" t="n">
-        <v>0.50469</v>
+        <v>0.79941005</v>
       </c>
       <c r="I31" t="n">
-        <v>0.22840999</v>
+        <v>0.05709</v>
       </c>
       <c r="J31" t="n">
-        <v>0.2495469603883098</v>
+        <v>0.1368511732071054</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.680560741319032</v>
+        <v>-0.3565429836616277</v>
       </c>
       <c r="L31" t="n">
-        <v>0.3666784538653364</v>
+        <v>0.3838279800142754</v>
       </c>
       <c r="M31" t="n">
-        <v>368638984192</v>
+        <v>25683312640</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2715,7 +2731,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Høj bruttomargin, positivt momentum, analytiker-upside over 20 %</t>
+          <t>Høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P31" t="n">
@@ -2725,14 +2741,14 @@
         <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>0.1371535722643684</v>
+        <v>0.2851676285900451</v>
       </c>
       <c r="S31" t="n">
-        <v>0.1829702280595702</v>
+        <v>0.1729552311683769</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2026-08-04 06:39:46</t>
+          <t>2026-08-09 07:56:42</t>
         </is>
       </c>
     </row>

--- a/data/compounder_radar.xlsx
+++ b/data/compounder_radar.xlsx
@@ -423,11 +423,11 @@
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
     <col width="23" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="23" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
     <col width="22" customWidth="1" min="12" max="12"/>
     <col width="17" customWidth="1" min="13" max="13"/>
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>86.40000000000001</v>
+        <v>86</v>
       </c>
       <c r="D2" t="n">
         <v>86</v>
@@ -577,16 +577,16 @@
         <v>0.14119</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2648009752477871</v>
+        <v>0.2162518358314054</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.3930142576986272</v>
+        <v>-0.4240016094960266</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6737693863789616</v>
+        <v>0.5100259786476871</v>
       </c>
       <c r="M2" t="n">
-        <v>237955268608</v>
+        <v>250756710400</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -605,33 +605,33 @@
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3310052780877977</v>
+        <v>0.3451052743939327</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4663091696109241</v>
+        <v>0.4714329078519075</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-08-09 07:56:42</t>
+          <t>2026-08-16 07:35:03</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>Booking Holdings Inc. Common St</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>81.2</v>
+        <v>79.8</v>
       </c>
       <c r="D3" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -639,28 +639,28 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.000450949944396</v>
+        <v>0.1634869878187224</v>
       </c>
       <c r="G3" t="n">
-        <v>2.04239508347386</v>
+        <v>0.2943673092572356</v>
       </c>
       <c r="H3" t="n">
-        <v>0.74144995</v>
+        <v>0.87227994</v>
       </c>
       <c r="I3" t="n">
-        <v>0.52727</v>
+        <v>0.2038</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3521502946954813</v>
+        <v>0.1214069602942565</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.2674138238971245</v>
+        <v>-0.2919928322172971</v>
       </c>
       <c r="L3" t="n">
-        <v>1.316873935548505</v>
+        <v>0.4157874677002587</v>
       </c>
       <c r="M3" t="n">
-        <v>5424535306240</v>
+        <v>164320722944</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -679,62 +679,60 @@
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.06014672155350387</v>
+        <v>0.376185286416532</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3045914419713429</v>
+        <v>0.2807943570289873</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-08-09 07:56:42</t>
+          <t>2026-08-16 07:35:03</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Micron Technology, Inc.</t>
+          <t>Palantir Technologies Inc.</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>77.40000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="D4" t="n">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>High Conviction</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.06713489726936261</v>
-      </c>
-      <c r="G4" t="n">
-        <v>-0.006929629272242499</v>
-      </c>
+        <v>0.3291712528765784</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.7256899999999999</v>
+        <v>0.84796</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3487</v>
+        <v>0.17292999</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7115178276376812</v>
+        <v>0.1013560101126179</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.8707111683398475</v>
+        <v>-0.3888186623764651</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8171686013793824</v>
+        <v>0.2606768139500519</v>
       </c>
       <c r="M4" t="n">
-        <v>991121571840</v>
+        <v>418228273152</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -743,72 +741,72 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Høj bruttomargin, positivt momentum, analytiker-upside over 20 %</t>
+          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="Q4" t="b">
         <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3573526703199177</v>
+        <v>0.3014282423273322</v>
       </c>
       <c r="S4" t="n">
-        <v>1.293279161436129</v>
+        <v>0.3477889468375444</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-08-09 07:56:42</t>
+          <t>2026-08-16 07:35:03</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices, Inc.</t>
+          <t>Micron Technology, Inc.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>76</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>High Conviction</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.1364359933536843</v>
+        <v>0.06713489726936261</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4666355102918431</v>
+        <v>-0.006929629272242499</v>
       </c>
       <c r="H5" t="n">
-        <v>0.55724</v>
+        <v>0.7256899999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05128</v>
+        <v>0.3487</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2688985435286328</v>
+        <v>0.5457842249346478</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.6912859980139027</v>
+        <v>-0.88323075973077</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3889830609923983</v>
+        <v>0.6179406898158937</v>
       </c>
       <c r="M5" t="n">
-        <v>789073100800</v>
+        <v>1097386098688</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -817,7 +815,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
+          <t>Høj bruttomargin, positivt momentum, analytiker-upside over 20 %</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -827,66 +825,66 @@
         <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1833716776756134</v>
+        <v>0.2523155524778455</v>
       </c>
       <c r="S5" t="n">
-        <v>1.51096096286526</v>
+        <v>1.348521979631764</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-08-09 07:56:42</t>
+          <t>2026-08-16 07:35:03</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Fortinet, Inc.</t>
+          <t>ServiceNow, Inc.</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FTNT</t>
+          <t>NOW</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>75.5</v>
+        <v>73.7</v>
       </c>
       <c r="D6" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>High Conviction</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.1546194776009138</v>
+        <v>0.2237651786474262</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3167495145145989</v>
+        <v>0.7345580184539504</v>
       </c>
       <c r="H6" t="n">
-        <v>0.80204004</v>
+        <v>0.74768996</v>
       </c>
       <c r="I6" t="n">
-        <v>0.14166</v>
+        <v>0.04249</v>
       </c>
       <c r="J6" t="n">
-        <v>0.007672575795540038</v>
+        <v>0.133700806451613</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5392758707090954</v>
+        <v>-0.3448387096774194</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01422755256127322</v>
+        <v>0.3877198316183351</v>
       </c>
       <c r="M6" t="n">
-        <v>117130051584</v>
+        <v>128198893568</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -901,33 +899,33 @@
         <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4785588365728168</v>
+        <v>0.3701657458563536</v>
       </c>
       <c r="S6" t="n">
-        <v>1.022551612471996</v>
+        <v>0.2005034262843091</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-08-09 07:56:42</t>
+          <t>2026-08-16 07:35:03</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Amphenol Corporation</t>
+          <t>Sandisk Corporation</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>APH</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>74.90000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="D7" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -935,28 +933,26 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.2230660589034148</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.2972340671812952</v>
-      </c>
+        <v>0.09932312697218015</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>0.38952</v>
+        <v>0.71474</v>
       </c>
       <c r="I7" t="n">
-        <v>0.14473</v>
+        <v>0.43910998</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1706987823619812</v>
+        <v>0.284310984638446</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.3810734129329708</v>
+        <v>-0.9736751345126164</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4479419885217928</v>
+        <v>0.291997787106642</v>
       </c>
       <c r="M7" t="n">
-        <v>208596123648</v>
+        <v>239602057216</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -965,43 +961,43 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, positivt momentum</t>
+          <t>Høj bruttomargin, positivt momentum, analytiker-upside over 20 %</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="Q7" t="b">
         <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2401934174574814</v>
+        <v>0.1868708199224489</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3301740732320491</v>
+        <v>1.603738029419161</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-08-09 07:56:42</t>
+          <t>2026-08-16 07:35:03</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Broadcom Inc.</t>
+          <t>Advanced Micro Devices, Inc.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>74.8</v>
+        <v>72.7</v>
       </c>
       <c r="D8" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1009,32 +1005,32 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.2437842600004176</v>
+        <v>0.1364359933536843</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2159817111378917</v>
+        <v>0.4666355102918431</v>
       </c>
       <c r="H8" t="n">
-        <v>0.76284</v>
+        <v>0.55724</v>
       </c>
       <c r="I8" t="n">
-        <v>0.121190004</v>
+        <v>0.05128</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2340669066766412</v>
+        <v>0.1913884406773072</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.3410557321862726</v>
+        <v>-0.7099088240440132</v>
       </c>
       <c r="L8" t="n">
-        <v>0.686301048735349</v>
+        <v>0.2695958046937045</v>
       </c>
       <c r="M8" t="n">
-        <v>2035102646272</v>
+        <v>839728824320</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1049,33 +1045,33 @@
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0.03848414109854015</v>
+        <v>0.143851458050716</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3826792124922158</v>
+        <v>1.497766381229363</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-08-09 07:56:42</t>
+          <t>2026-08-16 07:35:03</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc.</t>
+          <t>Fortinet, Inc.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>FTNT</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>74.7</v>
+        <v>72.7</v>
       </c>
       <c r="D9" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1083,26 +1079,28 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.3291712528765784</v>
-      </c>
-      <c r="G9" t="inlineStr"/>
+        <v>0.1546194776009138</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.3167495145145989</v>
+      </c>
       <c r="H9" t="n">
-        <v>0.84796</v>
+        <v>0.80204004</v>
       </c>
       <c r="I9" t="n">
-        <v>0.17292999</v>
+        <v>0.14166</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1040184872972503</v>
+        <v>0.005342478595087741</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.3816057205976396</v>
+        <v>-0.5403412286732079</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2725810481413775</v>
+        <v>0.009887231089521043</v>
       </c>
       <c r="M9" t="n">
-        <v>413350068224</v>
+        <v>117401518080</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -1111,43 +1109,43 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="Q9" t="b">
         <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2550893154075689</v>
+        <v>0.3130641203463418</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3230520865670188</v>
+        <v>0.8990029723490141</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-08-09 07:56:42</t>
+          <t>2026-08-16 07:35:03</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Booking Holdings Inc. Common St</t>
+          <t>DexCom, Inc.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>DXCM</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>74</v>
+        <v>72.5</v>
       </c>
       <c r="D10" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1155,32 +1153,32 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.1634869878187224</v>
+        <v>0.1701360960301399</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2943673092572356</v>
+        <v>0.365979383233586</v>
       </c>
       <c r="H10" t="n">
-        <v>0.87227994</v>
+        <v>0.62473</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2038</v>
+        <v>0.103310004</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1069914653483817</v>
+        <v>0.04869080779944301</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.2997854677735287</v>
+        <v>-0.3971030640668524</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3568934349719974</v>
+        <v>0.1226150392817063</v>
       </c>
       <c r="M10" t="n">
-        <v>166149439488</v>
+        <v>33868128256</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1195,33 +1193,33 @@
         <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2550153802075548</v>
+        <v>0.5522310701090165</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2121822677669754</v>
+        <v>0.3790718726927471</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-08-09 07:56:42</t>
+          <t>2026-08-16 07:35:03</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ServiceNow, Inc.</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NOW</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>73.40000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="D11" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1229,28 +1227,28 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.2237651786474262</v>
+        <v>0.1612397915820203</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7345580184539504</v>
+        <v>0.2285599828574523</v>
       </c>
       <c r="H11" t="n">
-        <v>0.74768996</v>
+        <v>0.67944</v>
       </c>
       <c r="I11" t="n">
-        <v>0.04249</v>
+        <v>0.14088</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1231007367072392</v>
+        <v>0.1496937828017764</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.3494554772581678</v>
+        <v>-0.2951150585385547</v>
       </c>
       <c r="L11" t="n">
-        <v>0.352264436296976</v>
+        <v>0.5072387140902874</v>
       </c>
       <c r="M11" t="n">
-        <v>129108688896</v>
+        <v>3678615371776</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1269,33 +1267,33 @@
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3343306137395301</v>
+        <v>0.2125955025570307</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2167982129538544</v>
+        <v>0.2383191571909435</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-08-09 07:56:42</t>
+          <t>2026-08-16 07:35:03</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DexCom, Inc.</t>
+          <t>Amphenol Corporation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DXCM</t>
+          <t>APH</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>72</v>
+        <v>71.3</v>
       </c>
       <c r="D12" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1303,28 +1301,28 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.1701360960301399</v>
+        <v>0.2230660589034148</v>
       </c>
       <c r="G12" t="n">
-        <v>0.365979383233586</v>
+        <v>0.2972340671812952</v>
       </c>
       <c r="H12" t="n">
-        <v>0.62473</v>
+        <v>0.38952</v>
       </c>
       <c r="I12" t="n">
-        <v>0.103310004</v>
+        <v>0.14473</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1025368731563421</v>
+        <v>0.1852002872359522</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.3615339233038348</v>
+        <v>-0.373406738076716</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2836161879895558</v>
+        <v>0.4959746794871789</v>
       </c>
       <c r="M12" t="n">
-        <v>31981324288</v>
+        <v>206043856896</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1333,7 +1331,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, positivt momentum</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -1343,33 +1341,33 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3913971468118593</v>
+        <v>0.2954726383578024</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2126198417531036</v>
+        <v>0.1667215312480956</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-08-09 07:56:42</t>
+          <t>2026-08-16 07:35:03</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>DoorDash, Inc.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>DASH</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>71.59999999999999</v>
+        <v>70.3</v>
       </c>
       <c r="D13" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1377,28 +1375,26 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.1612397915820203</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.2285599828574523</v>
-      </c>
+        <v>0.2772574009717286</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0.67944</v>
+        <v>0.52225</v>
       </c>
       <c r="I13" t="n">
-        <v>0.14088</v>
+        <v>0.029719999</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1267206544130883</v>
+        <v>0.1609090406414155</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.3015860317206345</v>
+        <v>-0.3396921942678094</v>
       </c>
       <c r="L13" t="n">
-        <v>0.4201807812189138</v>
+        <v>0.4736907216494846</v>
       </c>
       <c r="M13" t="n">
-        <v>3712698548224</v>
+        <v>94033821696</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1407,43 +1403,43 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
+          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="Q13" t="b">
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0.1908475313223374</v>
+        <v>0.4119714286366674</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2757298821491341</v>
+        <v>0.346779229827912</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-08-09 07:56:42</t>
+          <t>2026-08-16 07:35:03</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Datadog, Inc.</t>
+          <t>Seagate Technology Holdings PLC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>STX</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>71.2</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1451,26 +1447,26 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.2694953937625746</v>
+        <v>0.1820341908356484</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0.79536</v>
+        <v>0.45576</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0018000001</v>
+        <v>0.29354998</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1946964476552815</v>
+        <v>0.1463157462195923</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.5810285128029753</v>
+        <v>-0.8433390861275477</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3350893172454384</v>
+        <v>0.1734957487757935</v>
       </c>
       <c r="M14" t="n">
-        <v>83998416896</v>
+        <v>220970876928</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1489,14 +1485,14 @@
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0.2394955649418622</v>
+        <v>0.2104653587074417</v>
       </c>
       <c r="S14" t="n">
-        <v>1.191792235717045</v>
+        <v>1.263221740824967</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-08-09 07:56:42</t>
+          <t>2026-08-16 07:35:03</t>
         </is>
       </c>
     </row>
@@ -1512,10 +1508,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>71</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1535,16 +1531,16 @@
         <v>0.20357001</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0900853497060834</v>
+        <v>0.1107809957971799</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.4721306221588754</v>
+        <v>-0.4194431263557484</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1908059877458426</v>
+        <v>0.264114462334094</v>
       </c>
       <c r="M15" t="n">
-        <v>1056890945536</v>
+        <v>1051943960576</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1563,33 +1559,33 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0.2182561529182798</v>
+        <v>0.176006400246006</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1654455488311153</v>
+        <v>0.1421514318313866</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-08-09 07:56:42</t>
+          <t>2026-08-16 07:35:03</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Seagate Technology Holdings PLC</t>
+          <t>Expedia Group, Inc.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>STX</t>
+          <t>EXPE</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>68.7</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1597,26 +1593,28 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0.1820341908356484</v>
-      </c>
-      <c r="G16" t="inlineStr"/>
+        <v>0.08087962506974211</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.6534957812135467</v>
+      </c>
       <c r="H16" t="n">
-        <v>0.45576</v>
+        <v>0.90433</v>
       </c>
       <c r="I16" t="n">
-        <v>0.29354998</v>
+        <v>0.061079998</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3729386288695309</v>
+        <v>0.003508220866271783</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.8139303115310793</v>
+        <v>-0.4429048062761128</v>
       </c>
       <c r="L16" t="n">
-        <v>0.4581947908636039</v>
+        <v>0.00792093654563936</v>
       </c>
       <c r="M16" t="n">
-        <v>184496521216</v>
+        <v>39929237504</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1625,43 +1623,43 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="Q16" t="b">
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0.06119135769116801</v>
+        <v>0.5351860990956465</v>
       </c>
       <c r="S16" t="n">
-        <v>1.009516040690849</v>
+        <v>0.4703381198015009</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-08-09 07:56:42</t>
+          <t>2026-08-16 07:35:03</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Interactive Brokers Group, Inc.</t>
+          <t>Moody's Corporation</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>IBKR</t>
+          <t>MCO</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>69.5</v>
+        <v>67.5</v>
       </c>
       <c r="D17" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1669,32 +1667,32 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0.3459787421885367</v>
+        <v>0.1217396973837406</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3328887406583814</v>
+        <v>0.2248000431974093</v>
       </c>
       <c r="H17" t="n">
-        <v>0.93036</v>
+        <v>0.74974996</v>
       </c>
       <c r="I17" t="n">
-        <v>0.022839999</v>
+        <v>0.15619999</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2083949675509507</v>
+        <v>0.1557163477400196</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.3288170329044745</v>
+        <v>-0.1704882876938304</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6337718144044321</v>
+        <v>0.9133551040154806</v>
       </c>
       <c r="M17" t="n">
-        <v>149646131200</v>
+        <v>83985850368</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1709,33 +1707,33 @@
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0.05028029086934649</v>
+        <v>0.1258771223507436</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2665621031697569</v>
+        <v>0.1761241854329416</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-08-09 07:56:42</t>
+          <t>2026-08-16 07:35:03</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Marvell Technology, Inc.</t>
+          <t>Veeva Systems Inc.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>69.40000000000001</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1743,26 +1741,28 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0.1144958764235571</v>
-      </c>
-      <c r="G18" t="inlineStr"/>
+        <v>0.1402968452680178</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.2194365698361114</v>
+      </c>
       <c r="H18" t="n">
-        <v>0.5150299699999999</v>
+        <v>0.75021005</v>
       </c>
       <c r="I18" t="n">
-        <v>0.03808</v>
+        <v>0.07298</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1746260058522311</v>
+        <v>0.001611692307692314</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.7190929041697147</v>
+        <v>-0.3926153846153846</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2428420651068158</v>
+        <v>0.004105015673981208</v>
       </c>
       <c r="M18" t="n">
-        <v>196310925312</v>
+        <v>39595552768</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1771,43 +1771,43 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="Q18" t="b">
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3672517932141015</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="S18" t="n">
-        <v>1.94951442905662</v>
+        <v>0.4172335148258839</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-08-09 07:56:42</t>
+          <t>2026-08-16 07:35:03</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Axon Enterprise, Inc.</t>
+          <t>Datadog, Inc.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AXON</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>67.90000000000001</v>
+        <v>67.3</v>
       </c>
       <c r="D19" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1815,28 +1815,26 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0.3278726393918761</v>
-      </c>
-      <c r="G19" t="n">
-        <v>-0.09393302099393697</v>
-      </c>
+        <v>0.2694953937625746</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>0.5952499999999999</v>
+        <v>0.79536</v>
       </c>
       <c r="I19" t="n">
-        <v>0.00509</v>
+        <v>0.0018000001</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2115816885868897</v>
+        <v>0.1163399358020825</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.4062976130015237</v>
+        <v>-0.6163391529006498</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5207554310344823</v>
+        <v>0.1887596062241981</v>
       </c>
       <c r="M19" t="n">
-        <v>46387376128</v>
+        <v>91729305600</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1849,39 +1847,39 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="Q19" t="b">
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3376045121033731</v>
+        <v>0.2594163445375053</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4287752245369121</v>
+        <v>1.025370746663871</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-08-09 07:56:42</t>
+          <t>2026-08-16 07:35:03</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>KLA Corporation</t>
+          <t>Interactive Brokers Group, Inc.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>IBKR</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>67.8</v>
+        <v>66.7</v>
       </c>
       <c r="D20" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1889,28 +1887,28 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0.09685534331651668</v>
+        <v>0.3459787421885367</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1148114331133121</v>
+        <v>0.3328887406583814</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6130100000000001</v>
+        <v>0.93036</v>
       </c>
       <c r="I20" t="n">
-        <v>0.20799999</v>
+        <v>0.022839999</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1652710615314723</v>
+        <v>0.1528712796002607</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5799101509262531</v>
+        <v>-0.3596567456006952</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2849942551746947</v>
+        <v>0.4250477197221384</v>
       </c>
       <c r="M20" t="n">
-        <v>258839986176</v>
+        <v>156853256192</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -1919,7 +1917,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P20" t="n">
@@ -1929,33 +1927,33 @@
         <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1249843058235034</v>
+        <v>0.04387452280963045</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4922324438519448</v>
+        <v>0.2626913345791608</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-08-09 07:56:42</t>
+          <t>2026-08-16 07:35:03</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Veeva Systems Inc.</t>
+          <t>Marvell Technology, Inc.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>66.3</v>
+        <v>64.7</v>
       </c>
       <c r="D21" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1963,28 +1961,26 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0.1402968452680178</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.2194365698361114</v>
-      </c>
+        <v>0.1144958764235571</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>0.75021005</v>
+        <v>0.5150299699999999</v>
       </c>
       <c r="I21" t="n">
-        <v>0.07298</v>
+        <v>0.03808</v>
       </c>
       <c r="J21" t="n">
-        <v>0.05932594263895519</v>
+        <v>0.1588559589226195</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.3576170434329847</v>
+        <v>-0.723268174038375</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1658923804901723</v>
+        <v>0.2196363183459956</v>
       </c>
       <c r="M21" t="n">
-        <v>37438308352</v>
+        <v>199272824832</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -1993,43 +1989,43 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
+          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="Q21" t="b">
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3698068423221583</v>
+        <v>0.2163148817331868</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2535762500379706</v>
+        <v>1.840162774049261</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-08-09 07:56:42</t>
+          <t>2026-08-16 07:35:03</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>United Airlines Holdings, Inc.</t>
+          <t>Axon Enterprise, Inc.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>UAL</t>
+          <t>AXON</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>65.5</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -2037,37 +2033,37 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0.09529134601036815</v>
+        <v>0.3278726393918761</v>
       </c>
       <c r="G22" t="n">
-        <v>0.6599631084110487</v>
+        <v>-0.09393302099393697</v>
       </c>
       <c r="H22" t="n">
-        <v>0.31816</v>
+        <v>0.5952499999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>0.03381</v>
+        <v>0.00509</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2515605125038591</v>
+        <v>0.1314789419578022</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.3467119481321396</v>
+        <v>-0.4468123296835991</v>
       </c>
       <c r="L22" t="n">
-        <v>0.7255605520926088</v>
+        <v>0.2942598787524648</v>
       </c>
       <c r="M22" t="n">
-        <v>42051252224</v>
+        <v>49784725504</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Stærk eps-vækst, positivt momentum, analytiker-upside over 20 %</t>
+          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P22" t="n">
@@ -2077,33 +2073,33 @@
         <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>0.2994985107758124</v>
+        <v>0.578685729245036</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2212272790165106</v>
+        <v>0.4061862291432403</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-08-09 07:56:42</t>
+          <t>2026-08-16 07:35:03</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Applied Materials, Inc.</t>
+          <t>Garmin Ltd.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>GRMN</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>65.3</v>
+        <v>64.3</v>
       </c>
       <c r="D23" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -2111,28 +2107,28 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0.03233470456886756</v>
+        <v>0.142358869424539</v>
       </c>
       <c r="G23" t="n">
-        <v>0.05191743203490939</v>
+        <v>0.1945038186480894</v>
       </c>
       <c r="H23" t="n">
-        <v>0.48956</v>
+        <v>0.60081</v>
       </c>
       <c r="I23" t="n">
-        <v>0.14858</v>
+        <v>0.12174</v>
       </c>
       <c r="J23" t="n">
-        <v>0.1667787587639575</v>
+        <v>-0.06419825918762079</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.7134881477909263</v>
+        <v>-0.39822695035461</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2337512673200407</v>
+        <v>-0.1612102323322267</v>
       </c>
       <c r="M23" t="n">
-        <v>428055298048</v>
+        <v>59823996928</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -2141,7 +2137,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P23" t="n">
@@ -2151,30 +2147,30 @@
         <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>0.3145583294175336</v>
+        <v>0.3290706526187623</v>
       </c>
       <c r="S23" t="n">
-        <v>0.7779648791718274</v>
+        <v>0.5390618576759405</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-08-09 07:56:42</t>
+          <t>2026-08-16 07:35:03</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc.</t>
+          <t>KLA Corporation</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>64.40000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="D24" t="n">
         <v>64</v>
@@ -2185,28 +2181,28 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0.03534983888485344</v>
+        <v>0.08964649002419045</v>
       </c>
       <c r="G24" t="n">
-        <v>0.388859258627138</v>
+        <v>0.1486507049039818</v>
       </c>
       <c r="H24" t="n">
-        <v>0.19212</v>
+        <v>0.6130100000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>0.07004000000000001</v>
+        <v>0.20799999</v>
       </c>
       <c r="J24" t="n">
-        <v>0.108012032527492</v>
+        <v>0.1377272236402907</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.757101615355797</v>
+        <v>-0.591478499901826</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1426651724639792</v>
+        <v>0.2328524598326917</v>
       </c>
       <c r="M24" t="n">
-        <v>293200035840</v>
+        <v>266169712640</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -2215,7 +2211,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Stærk eps-vækst, positivt momentum</t>
+          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P24" t="n">
@@ -2225,30 +2221,30 @@
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9738559714176462</v>
+        <v>0.07758302643336323</v>
       </c>
       <c r="S24" t="n">
-        <v>2.951175825528565</v>
+        <v>0.4077612800205148</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-08-09 07:56:42</t>
+          <t>2026-08-16 07:35:03</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Howmet Aerospace Inc.</t>
+          <t>Lam Research Corporation</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>HWM</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>64.3</v>
+        <v>64</v>
       </c>
       <c r="D25" t="n">
         <v>64</v>
@@ -2259,28 +2255,28 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0.1337158522423005</v>
+        <v>0.1005582390165327</v>
       </c>
       <c r="G25" t="n">
-        <v>0.495146138791156</v>
+        <v>0.2014836612049711</v>
       </c>
       <c r="H25" t="n">
-        <v>0.36032</v>
+        <v>0.50469</v>
       </c>
       <c r="I25" t="n">
-        <v>0.12815</v>
+        <v>0.22840999</v>
       </c>
       <c r="J25" t="n">
-        <v>0.1363984674329501</v>
+        <v>0.1100478396919002</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.3988576699304669</v>
+        <v>-0.7168431820917078</v>
       </c>
       <c r="L25" t="n">
-        <v>0.3419727830650181</v>
+        <v>0.1535173137460649</v>
       </c>
       <c r="M25" t="n">
-        <v>112414146560</v>
+        <v>415889031168</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -2289,7 +2285,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P25" t="n">
@@ -2299,33 +2295,33 @@
         <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0.0352259372142707</v>
+        <v>0.111797107429453</v>
       </c>
       <c r="S25" t="n">
-        <v>0.3466684453814286</v>
+        <v>0.4397189508246566</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-08-09 07:56:42</t>
+          <t>2026-08-16 07:35:03</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Garmin Ltd.</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GRMN</t>
+          <t>GE</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>64</v>
+        <v>63.1</v>
       </c>
       <c r="D26" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -2333,37 +2329,37 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0.142358869424539</v>
+        <v>0.1631543559703441</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1945038186480894</v>
+        <v>4.460320482827598</v>
       </c>
       <c r="H26" t="n">
-        <v>0.60081</v>
+        <v>0.31051</v>
       </c>
       <c r="I26" t="n">
-        <v>0.12174</v>
+        <v>0.05065</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.06627520988130842</v>
+        <v>0.09914965524729902</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.3995625462382193</v>
+        <v>-0.2838916336391769</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.165869425213331</v>
+        <v>0.3492517689806848</v>
       </c>
       <c r="M26" t="n">
-        <v>59957067776</v>
+        <v>382217289728</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, positivt momentum</t>
         </is>
       </c>
       <c r="P26" t="n">
@@ -2373,33 +2369,33 @@
         <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>0.2908933123836939</v>
+        <v>0.2651408771769854</v>
       </c>
       <c r="S26" t="n">
-        <v>0.5776529045416638</v>
+        <v>0.1805314754252272</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-08-09 07:56:42</t>
+          <t>2026-08-16 07:35:03</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise Comp</t>
+          <t>United Airlines Holdings, Inc.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>HPE</t>
+          <t>UAL</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>63.8</v>
+        <v>62.9</v>
       </c>
       <c r="D27" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -2407,71 +2403,73 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>0.06370170685761956</v>
-      </c>
-      <c r="G27" t="inlineStr"/>
+        <v>0.09529134601036815</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.6599631084110487</v>
+      </c>
       <c r="H27" t="n">
-        <v>0.33776</v>
+        <v>0.31816</v>
       </c>
       <c r="I27" t="n">
-        <v>0.01966</v>
+        <v>0.03381</v>
       </c>
       <c r="J27" t="n">
-        <v>0.2318183013904549</v>
+        <v>0.2936985798627731</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.6272078166102969</v>
+        <v>-0.324716770384554</v>
       </c>
       <c r="L27" t="n">
-        <v>0.3696036548831638</v>
+        <v>0.9044761670761666</v>
       </c>
       <c r="M27" t="n">
-        <v>70474113024</v>
+        <v>40681570304</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Positivt momentum, analytiker-upside over 20 %</t>
+          <t>Stærk eps-vækst, positivt momentum, analytiker-upside over 20 %</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="Q27" t="b">
         <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>0.7971617803249145</v>
+        <v>0.3053530589447424</v>
       </c>
       <c r="S27" t="n">
-        <v>1.365472550960148</v>
+        <v>0.1467519930309358</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-08-09 07:56:42</t>
+          <t>2026-08-16 07:35:03</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>F5, Inc.</t>
+          <t>Corpay, Inc.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>63.3</v>
+        <v>62.4</v>
       </c>
       <c r="D28" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -2479,28 +2477,28 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>0.04631913174341684</v>
+        <v>0.097332408585459</v>
       </c>
       <c r="G28" t="n">
-        <v>0.3082491584064506</v>
+        <v>0.06564477917470324</v>
       </c>
       <c r="H28" t="n">
-        <v>0.81865996</v>
+        <v>0.8053900000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>0.07976999999999999</v>
+        <v>0.06315999999999999</v>
       </c>
       <c r="J28" t="n">
-        <v>0.08962346650675856</v>
+        <v>0.07912559865900382</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.4409214701546611</v>
+        <v>-0.3945402298850575</v>
       </c>
       <c r="L28" t="n">
-        <v>0.2032640108800362</v>
+        <v>0.2005514081087642</v>
       </c>
       <c r="M28" t="n">
-        <v>22663899136</v>
+        <v>27419449344</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2509,7 +2507,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
+          <t>Høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P28" t="n">
@@ -2519,33 +2517,33 @@
         <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>0.1600197777829866</v>
+        <v>0.2686453475969344</v>
       </c>
       <c r="S28" t="n">
-        <v>0.4757200088353686</v>
+        <v>0.2996389785406306</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-08-09 07:56:42</t>
+          <t>2026-08-16 07:35:03</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Expedia Group, Inc.</t>
+          <t>Incyte Corporation</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>EXPE</t>
+          <t>INCY</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>63.3</v>
+        <v>62.2</v>
       </c>
       <c r="D29" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -2553,37 +2551,37 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>0.08087962506974211</v>
+        <v>0.1483959547833886</v>
       </c>
       <c r="G29" t="n">
-        <v>0.6534957812135467</v>
+        <v>0.6156160063417289</v>
       </c>
       <c r="H29" t="n">
-        <v>0.90433</v>
+        <v>0.55659</v>
       </c>
       <c r="I29" t="n">
-        <v>0.061079998</v>
+        <v>0.16832</v>
       </c>
       <c r="J29" t="n">
-        <v>0.02383713145358568</v>
+        <v>0.04172694740346206</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.4034376207029742</v>
+        <v>-0.3251498002663116</v>
       </c>
       <c r="L29" t="n">
-        <v>0.05908504866762405</v>
+        <v>0.1283314563603788</v>
       </c>
       <c r="M29" t="n">
-        <v>37287608320</v>
+        <v>24356161536</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P29" t="n">
@@ -2593,30 +2591,30 @@
         <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>0.2316136480683892</v>
+        <v>0.2307693029040072</v>
       </c>
       <c r="S29" t="n">
-        <v>0.3489626342686869</v>
+        <v>0.1926551231971154</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2026-08-09 07:56:42</t>
+          <t>2026-08-16 07:35:03</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gen Digital Inc.</t>
+          <t>Delta Air Lines, Inc.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>62.5</v>
+        <v>62</v>
       </c>
       <c r="D30" t="n">
         <v>62</v>
@@ -2627,28 +2625,28 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>0.1465900735417971</v>
+        <v>0.07799197884220499</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.09938459624739093</v>
+        <v>0.5492464741024845</v>
       </c>
       <c r="H30" t="n">
-        <v>0.7800700699999999</v>
+        <v>0.187</v>
       </c>
       <c r="I30" t="n">
-        <v>0.084910005</v>
+        <v>0.04019</v>
       </c>
       <c r="J30" t="n">
-        <v>0.05611930065135406</v>
+        <v>0.1809829882484613</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.3904696606102159</v>
+        <v>-0.3841074426412983</v>
       </c>
       <c r="L30" t="n">
-        <v>0.1437225636523264</v>
+        <v>0.4711780303030307</v>
       </c>
       <c r="M30" t="n">
-        <v>17460494336</v>
+        <v>58758619136</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2657,7 +2655,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk eps-vækst, positivt momentum</t>
         </is>
       </c>
       <c r="P30" t="n">
@@ -2667,30 +2665,30 @@
         <v>1</v>
       </c>
       <c r="R30" t="n">
-        <v>0.4525172025700568</v>
+        <v>0.2518604017507877</v>
       </c>
       <c r="S30" t="n">
-        <v>0.3144366553078433</v>
+        <v>0.2957160641454124</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2026-08-09 07:56:42</t>
+          <t>2026-08-16 07:35:03</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Corpay, Inc.</t>
+          <t>F5, Inc.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CPAY</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>62.3</v>
+        <v>61.9</v>
       </c>
       <c r="D31" t="n">
         <v>62</v>
@@ -2701,28 +2699,28 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>0.097332408585459</v>
+        <v>0.04631913174341684</v>
       </c>
       <c r="G31" t="n">
-        <v>0.06564477917470324</v>
+        <v>0.3082491584064506</v>
       </c>
       <c r="H31" t="n">
-        <v>0.79941005</v>
+        <v>0.81865996</v>
       </c>
       <c r="I31" t="n">
-        <v>0.05709</v>
+        <v>0.07976999999999999</v>
       </c>
       <c r="J31" t="n">
-        <v>0.1368511732071054</v>
+        <v>0.08159722222222232</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.3565429836616277</v>
+        <v>-0.4450396825396825</v>
       </c>
       <c r="L31" t="n">
-        <v>0.3838279800142754</v>
+        <v>0.1833481943825236</v>
       </c>
       <c r="M31" t="n">
-        <v>25683312640</v>
+        <v>22832080896</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2731,7 +2729,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Høj bruttomargin, positivt momentum</t>
+          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P31" t="n">
@@ -2741,14 +2739,14 @@
         <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>0.2851676285900451</v>
+        <v>0.1058998224223302</v>
       </c>
       <c r="S31" t="n">
-        <v>0.1729552311683769</v>
+        <v>0.5388139421149001</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2026-08-09 07:56:42</t>
+          <t>2026-08-16 07:35:03</t>
         </is>
       </c>
     </row>

--- a/data/compounder_radar.xlsx
+++ b/data/compounder_radar.xlsx
@@ -423,19 +423,19 @@
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
     <col width="23" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="23" customWidth="1" min="12" max="12"/>
     <col width="17" customWidth="1" min="13" max="13"/>
     <col width="8" customWidth="1" min="14" max="14"/>
     <col width="45" customWidth="1" min="15" max="15"/>
     <col width="19" customWidth="1" min="16" max="16"/>
     <col width="18" customWidth="1" min="17" max="17"/>
-    <col width="22" customWidth="1" min="18" max="18"/>
+    <col width="23" customWidth="1" min="18" max="18"/>
     <col width="21" customWidth="1" min="19" max="19"/>
     <col width="21" customWidth="1" min="20" max="20"/>
   </cols>
@@ -554,10 +554,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>86</v>
+        <v>84.3</v>
       </c>
       <c r="D2" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -577,16 +577,16 @@
         <v>0.14119</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2162518358314054</v>
+        <v>0.2818191889742909</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.4240016094960266</v>
+        <v>-0.3929499072356215</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5100259786476871</v>
+        <v>0.7171885876163494</v>
       </c>
       <c r="M2" t="n">
-        <v>250756710400</v>
+        <v>237930037248</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -605,14 +605,14 @@
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3451052743939327</v>
+        <v>0.2696009054842301</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4714329078519075</v>
+        <v>0.4206642325072321</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-08-16 07:35:03</t>
+          <t>2026-08-23 07:36:41</t>
         </is>
       </c>
     </row>
@@ -628,10 +628,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>79.8</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -651,16 +651,16 @@
         <v>0.2038</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1214069602942565</v>
+        <v>0.1344602614254367</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.2919928322172971</v>
+        <v>-0.2837515504245779</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4157874677002587</v>
+        <v>0.4738661735036991</v>
       </c>
       <c r="M3" t="n">
-        <v>164320722944</v>
+        <v>162430025728</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -679,60 +679,60 @@
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.376185286416532</v>
+        <v>0.3160507220066857</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2807943570289873</v>
+        <v>0.2916188965059978</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-08-16 07:35:03</t>
+          <t>2026-08-23 07:36:41</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc.</t>
+          <t>Sandisk Corporation</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>74.7</v>
+        <v>75.2</v>
       </c>
       <c r="D4" t="n">
         <v>71</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>High Conviction</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.3291712528765784</v>
+        <v>0.4928519097558826</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.84796</v>
+        <v>0.71474</v>
       </c>
       <c r="I4" t="n">
-        <v>0.17292999</v>
+        <v>0.43910998</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1013560101126179</v>
+        <v>0.3321223246955041</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.3888186623764651</v>
+        <v>-0.9711731241541778</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2606768139500519</v>
+        <v>0.3419805557168387</v>
       </c>
       <c r="M4" t="n">
-        <v>418228273152</v>
+        <v>233696444416</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -751,14 +751,14 @@
         <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3014282423273322</v>
+        <v>0.03491023845914576</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3477889468375444</v>
+        <v>1.455621071736712</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-08-16 07:35:03</t>
+          <t>2026-08-23 07:36:41</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>73.90000000000001</v>
+        <v>74.5</v>
       </c>
       <c r="D5" t="n">
         <v>74</v>
@@ -797,16 +797,16 @@
         <v>0.3487</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5457842249346478</v>
+        <v>0.5671751587744884</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.88323075973077</v>
+        <v>-0.8818241999213885</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6179406898158937</v>
+        <v>0.643183934876192</v>
       </c>
       <c r="M5" t="n">
-        <v>1097386098688</v>
+        <v>1091874717696</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -825,33 +825,33 @@
         <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2523155524778455</v>
+        <v>0.2687688546422129</v>
       </c>
       <c r="S5" t="n">
-        <v>1.348521979631764</v>
+        <v>1.259231023662006</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-08-16 07:35:03</t>
+          <t>2026-08-23 07:36:41</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ServiceNow, Inc.</t>
+          <t>Robinhood Markets, Inc.</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NOW</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>73.7</v>
+        <v>74.2</v>
       </c>
       <c r="D6" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -859,73 +859,71 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.2237651786474262</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.7345580184539504</v>
-      </c>
+        <v>0.4878747583673768</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>0.74768996</v>
+        <v>0.9189000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.04249</v>
+        <v>0.04528</v>
       </c>
       <c r="J6" t="n">
-        <v>0.133700806451613</v>
+        <v>0.1091350226579118</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.3448387096774194</v>
+        <v>-0.4126051974475169</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3877198316183351</v>
+        <v>0.2645022974335985</v>
       </c>
       <c r="M6" t="n">
-        <v>128198893568</v>
+        <v>97217765376</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
+          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="Q6" t="b">
         <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3701657458563536</v>
+        <v>0.4242623796275062</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2005034262843091</v>
+        <v>0.420706824153033</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-08-16 07:35:03</t>
+          <t>2026-08-23 07:36:41</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sandisk Corporation</t>
+          <t>Expedia Group, Inc.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>EXPE</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>73.3</v>
+        <v>73</v>
       </c>
       <c r="D7" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -933,26 +931,28 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.09932312697218015</v>
-      </c>
-      <c r="G7" t="inlineStr"/>
+        <v>0.08087962506974211</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.6534957812135467</v>
+      </c>
       <c r="H7" t="n">
-        <v>0.71474</v>
+        <v>0.90433</v>
       </c>
       <c r="I7" t="n">
-        <v>0.43910998</v>
+        <v>0.061079998</v>
       </c>
       <c r="J7" t="n">
-        <v>0.284310984638446</v>
+        <v>0.04538936044523223</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.9736751345126164</v>
+        <v>-0.4237477847215745</v>
       </c>
       <c r="L7" t="n">
-        <v>0.291997787106642</v>
+        <v>0.1071140949446037</v>
       </c>
       <c r="M7" t="n">
-        <v>239602057216</v>
+        <v>38601822208</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -961,43 +961,43 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Høj bruttomargin, positivt momentum, analytiker-upside over 20 %</t>
+          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="Q7" t="b">
         <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1868708199224489</v>
+        <v>0.4776859946775289</v>
       </c>
       <c r="S7" t="n">
-        <v>1.603738029419161</v>
+        <v>0.5874392660754975</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-08-16 07:35:03</t>
+          <t>2026-08-23 07:36:41</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices, Inc.</t>
+          <t>Eli Lilly and Company</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>72.7</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1005,28 +1005,28 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.1364359933536843</v>
+        <v>0.3168737488062043</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4666355102918431</v>
+        <v>0.5171329563234539</v>
       </c>
       <c r="H8" t="n">
-        <v>0.55724</v>
+        <v>0.83399004</v>
       </c>
       <c r="I8" t="n">
-        <v>0.05128</v>
+        <v>0.20357001</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1913884406773072</v>
+        <v>0.04750724868567779</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.7099088240440132</v>
+        <v>-0.4470049386649674</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2695958046937045</v>
+        <v>0.1062790241816204</v>
       </c>
       <c r="M8" t="n">
-        <v>839728824320</v>
+        <v>1119009636352</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -1045,33 +1045,33 @@
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0.143851458050716</v>
+        <v>0.2069302535023232</v>
       </c>
       <c r="S8" t="n">
-        <v>1.497766381229363</v>
+        <v>0.2474871155709406</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-08-16 07:35:03</t>
+          <t>2026-08-23 07:36:41</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Fortinet, Inc.</t>
+          <t>Palantir Technologies Inc.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FTNT</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>72.7</v>
+        <v>72.3</v>
       </c>
       <c r="D9" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1079,28 +1079,26 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.1546194776009138</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.3167495145145989</v>
-      </c>
+        <v>0.3291712528765784</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>0.80204004</v>
+        <v>0.84796</v>
       </c>
       <c r="I9" t="n">
-        <v>0.14166</v>
+        <v>0.17292999</v>
       </c>
       <c r="J9" t="n">
-        <v>0.005342478595087741</v>
+        <v>0.06524397021229311</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5403412286732079</v>
+        <v>-0.4088585083916861</v>
       </c>
       <c r="L9" t="n">
-        <v>0.009887231089521043</v>
+        <v>0.1595759140954196</v>
       </c>
       <c r="M9" t="n">
-        <v>117401518080</v>
+        <v>432406331392</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -1109,40 +1107,40 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
+          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="Q9" t="b">
         <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3130641203463418</v>
+        <v>0.3094641140557755</v>
       </c>
       <c r="S9" t="n">
-        <v>0.8990029723490141</v>
+        <v>0.3305234777626627</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-08-16 07:35:03</t>
+          <t>2026-08-23 07:36:41</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DexCom, Inc.</t>
+          <t>Fortinet, Inc.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DXCM</t>
+          <t>FTNT</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>72.5</v>
+        <v>72.2</v>
       </c>
       <c r="D10" t="n">
         <v>72</v>
@@ -1153,28 +1151,28 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.1701360960301399</v>
+        <v>0.1546194776009138</v>
       </c>
       <c r="G10" t="n">
-        <v>0.365979383233586</v>
+        <v>0.3167495145145989</v>
       </c>
       <c r="H10" t="n">
-        <v>0.62473</v>
+        <v>0.80204004</v>
       </c>
       <c r="I10" t="n">
-        <v>0.103310004</v>
+        <v>0.14166</v>
       </c>
       <c r="J10" t="n">
-        <v>0.04869080779944301</v>
+        <v>0.04791121099602624</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.3971030640668524</v>
+        <v>-0.5208781186893362</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1226150392817063</v>
+        <v>0.09198161580790382</v>
       </c>
       <c r="M10" t="n">
-        <v>33868128256</v>
+        <v>112632381440</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1193,30 +1191,30 @@
         <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>0.5522310701090165</v>
+        <v>0.1857715629980159</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3790718726927471</v>
+        <v>0.9188749313354492</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-08-16 07:35:03</t>
+          <t>2026-08-23 07:36:41</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>ServiceNow, Inc.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>NOW</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>71.8</v>
+        <v>72</v>
       </c>
       <c r="D11" t="n">
         <v>72</v>
@@ -1227,32 +1225,32 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.1612397915820203</v>
+        <v>0.2237651786474262</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2285599828574523</v>
+        <v>0.7345580184539504</v>
       </c>
       <c r="H11" t="n">
-        <v>0.67944</v>
+        <v>0.74768996</v>
       </c>
       <c r="I11" t="n">
-        <v>0.14088</v>
+        <v>0.04249</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1496937828017764</v>
+        <v>0.107034090909091</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.2951150585385547</v>
+        <v>-0.3676836861768369</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5072387140902874</v>
+        <v>0.2911037256562238</v>
       </c>
       <c r="M11" t="n">
-        <v>3678615371776</v>
+        <v>132830584832</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1267,33 +1265,33 @@
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2125955025570307</v>
+        <v>0.288795190902462</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2383191571909435</v>
+        <v>0.2321856705083392</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-08-16 07:35:03</t>
+          <t>2026-08-23 07:36:41</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Amphenol Corporation</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>APH</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>71.3</v>
+        <v>71.7</v>
       </c>
       <c r="D12" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1301,37 +1299,37 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.2230660589034148</v>
+        <v>0.1612397915820203</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2972340671812952</v>
+        <v>0.2285599828574523</v>
       </c>
       <c r="H12" t="n">
-        <v>0.38952</v>
+        <v>0.67944</v>
       </c>
       <c r="I12" t="n">
-        <v>0.14473</v>
+        <v>0.14088</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1852002872359522</v>
+        <v>0.1784076235410976</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.373406738076716</v>
+        <v>-0.27737770052148</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4959746794871789</v>
+        <v>0.6431938227394808</v>
       </c>
       <c r="M12" t="n">
-        <v>206043856896</v>
+        <v>3588320657408</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -1341,33 +1339,33 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2954726383578024</v>
+        <v>0.155240445038888</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1667215312480956</v>
+        <v>0.2214543204099817</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-08-16 07:35:03</t>
+          <t>2026-08-23 07:36:41</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DoorDash, Inc.</t>
+          <t>Advanced Micro Devices, Inc.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DASH</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>70.3</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1375,52 +1373,54 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.2772574009717286</v>
-      </c>
-      <c r="G13" t="inlineStr"/>
+        <v>0.1364359933536843</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.4666355102918431</v>
+      </c>
       <c r="H13" t="n">
-        <v>0.52225</v>
+        <v>0.55724</v>
       </c>
       <c r="I13" t="n">
-        <v>0.029719999</v>
+        <v>0.05128</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1609090406414155</v>
+        <v>0.295492234548336</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.3396921942678094</v>
+        <v>-0.6846909667194929</v>
       </c>
       <c r="L13" t="n">
-        <v>0.4736907216494846</v>
+        <v>0.4315702249791685</v>
       </c>
       <c r="M13" t="n">
-        <v>94033821696</v>
+        <v>772568776704</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="Q13" t="b">
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0.4119714286366674</v>
+        <v>0.05262573423526007</v>
       </c>
       <c r="S13" t="n">
-        <v>0.346779229827912</v>
+        <v>1.364476714622136</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-08-16 07:35:03</t>
+          <t>2026-08-23 07:36:41</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="D14" t="n">
         <v>66</v>
@@ -1457,16 +1457,16 @@
         <v>0.29354998</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1463157462195923</v>
+        <v>0.3235294117647058</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.8433390861275477</v>
+        <v>-0.8133176470588235</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1734957487757935</v>
+        <v>0.3977897355783139</v>
       </c>
       <c r="M14" t="n">
-        <v>220970876928</v>
+        <v>192949993472</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1485,33 +1485,33 @@
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0.2104653587074417</v>
+        <v>0.0495348748175839</v>
       </c>
       <c r="S14" t="n">
-        <v>1.263221740824967</v>
+        <v>1.072656535508107</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-08-16 07:35:03</t>
+          <t>2026-08-23 07:36:41</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Eli Lilly and Company</t>
+          <t>Veeva Systems Inc.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>69.59999999999999</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1519,28 +1519,28 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0.3168737488062043</v>
+        <v>0.1402968452680178</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5171329563234539</v>
+        <v>0.2194365698361114</v>
       </c>
       <c r="H15" t="n">
-        <v>0.83399004</v>
+        <v>0.75021005</v>
       </c>
       <c r="I15" t="n">
-        <v>0.20357001</v>
+        <v>0.07298</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1107809957971799</v>
+        <v>0.02287789431222254</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.4194431263557484</v>
+        <v>-0.4027833803953207</v>
       </c>
       <c r="L15" t="n">
-        <v>0.264114462334094</v>
+        <v>0.05679949924887297</v>
       </c>
       <c r="M15" t="n">
-        <v>1051943960576</v>
+        <v>40269692928</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1559,30 +1559,30 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0.176006400246006</v>
+        <v>0.5663106539741156</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1421514318313866</v>
+        <v>0.3748544021577422</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-08-16 07:35:03</t>
+          <t>2026-08-23 07:36:41</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Expedia Group, Inc.</t>
+          <t>Interactive Brokers Group, Inc.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EXPE</t>
+          <t>IBKR</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>68.7</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="D16" t="n">
         <v>69</v>
@@ -1593,28 +1593,28 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0.08087962506974211</v>
+        <v>0.3459787421885367</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6534957812135467</v>
+        <v>0.3328887406583814</v>
       </c>
       <c r="H16" t="n">
-        <v>0.90433</v>
+        <v>0.93036</v>
       </c>
       <c r="I16" t="n">
-        <v>0.061079998</v>
+        <v>0.022839999</v>
       </c>
       <c r="J16" t="n">
-        <v>0.003508220866271783</v>
+        <v>0.1306416320443167</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.4429048062761128</v>
+        <v>-0.3720038350910834</v>
       </c>
       <c r="L16" t="n">
-        <v>0.00792093654563936</v>
+        <v>0.351183562428408</v>
       </c>
       <c r="M16" t="n">
-        <v>39929237504</v>
+        <v>159937167360</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -1633,30 +1633,30 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0.5351860990956465</v>
+        <v>0.1209003878050932</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4703381198015009</v>
+        <v>0.2643279441332309</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-08-16 07:35:03</t>
+          <t>2026-08-23 07:36:41</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Moody's Corporation</t>
+          <t>Dell Technologies Inc.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MCO</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>67.5</v>
+        <v>67.7</v>
       </c>
       <c r="D17" t="n">
         <v>68</v>
@@ -1667,37 +1667,37 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0.1217396973837406</v>
+        <v>0.03534983888485344</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2248000431974093</v>
+        <v>0.388859258627138</v>
       </c>
       <c r="H17" t="n">
-        <v>0.74974996</v>
+        <v>0.19212</v>
       </c>
       <c r="I17" t="n">
-        <v>0.15619999</v>
+        <v>0.07004000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1557163477400196</v>
+        <v>0.1508835957292798</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.1704882876938304</v>
+        <v>-0.7506786102062974</v>
       </c>
       <c r="L17" t="n">
-        <v>0.9133551040154806</v>
+        <v>0.200996263484602</v>
       </c>
       <c r="M17" t="n">
-        <v>83985850368</v>
+        <v>285646618624</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
+          <t>Stærk eps-vækst, positivt momentum</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -1707,26 +1707,26 @@
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0.1258771223507436</v>
+        <v>0.7516238195631495</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1761241854329416</v>
+        <v>2.632785198046367</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-08-16 07:35:03</t>
+          <t>2026-08-23 07:36:41</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Veeva Systems Inc.</t>
+          <t>Amphenol Corporation</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>APH</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1741,37 +1741,37 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0.1402968452680178</v>
+        <v>0.2230660589034148</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2194365698361114</v>
+        <v>0.2972340671812952</v>
       </c>
       <c r="H18" t="n">
-        <v>0.75021005</v>
+        <v>0.38952</v>
       </c>
       <c r="I18" t="n">
-        <v>0.07298</v>
+        <v>0.14473</v>
       </c>
       <c r="J18" t="n">
-        <v>0.001611692307692314</v>
+        <v>0.2236013629705116</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.3926153846153846</v>
+        <v>-0.3283867269600662</v>
       </c>
       <c r="L18" t="n">
-        <v>0.004105015673981208</v>
+        <v>0.6809086501163698</v>
       </c>
       <c r="M18" t="n">
-        <v>39595552768</v>
+        <v>193590722560</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, positivt momentum</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -1781,33 +1781,33 @@
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.2593854585494386</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4172335148258839</v>
+        <v>0.04315191881713076</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-08-16 07:35:03</t>
+          <t>2026-08-23 07:36:41</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Datadog, Inc.</t>
+          <t>Salesforce, Inc.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>67.3</v>
+        <v>66.8</v>
       </c>
       <c r="D19" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1815,71 +1815,73 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0.2694953937625746</v>
-      </c>
-      <c r="G19" t="inlineStr"/>
+        <v>0.09820006113830493</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2.336504917866317</v>
+      </c>
       <c r="H19" t="n">
-        <v>0.79536</v>
+        <v>0.77643996</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0018000001</v>
+        <v>0.05703</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1163399358020825</v>
+        <v>0.1664399770521585</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6163391529006498</v>
+        <v>-0.3004732992302911</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1887596062241981</v>
+        <v>0.5539260143198091</v>
       </c>
       <c r="M19" t="n">
-        <v>91729305600</v>
+        <v>171310235648</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="Q19" t="b">
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2594163445375053</v>
+        <v>0.1894382314755338</v>
       </c>
       <c r="S19" t="n">
-        <v>1.025370746663871</v>
+        <v>0.1354198866051552</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-08-16 07:35:03</t>
+          <t>2026-08-23 07:36:41</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Interactive Brokers Group, Inc.</t>
+          <t>DoorDash, Inc.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>IBKR</t>
+          <t>DASH</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>66.7</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1887,28 +1889,26 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0.3459787421885367</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.3328887406583814</v>
-      </c>
+        <v>0.2772574009717286</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>0.93036</v>
+        <v>0.52225</v>
       </c>
       <c r="I20" t="n">
-        <v>0.022839999</v>
+        <v>0.029719999</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1528712796002607</v>
+        <v>0.1288989216519754</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.3596567456006952</v>
+        <v>-0.3588080003579578</v>
       </c>
       <c r="L20" t="n">
-        <v>0.4250477197221384</v>
+        <v>0.3592420501309387</v>
       </c>
       <c r="M20" t="n">
-        <v>156853256192</v>
+        <v>96837246976</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -1917,43 +1917,43 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
+          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="Q20" t="b">
         <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>0.04387452280963045</v>
+        <v>0.4032146637658329</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2626913345791608</v>
+        <v>0.2677407340439446</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-08-16 07:35:03</t>
+          <t>2026-08-23 07:36:41</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Marvell Technology, Inc.</t>
+          <t>DexCom, Inc.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>DXCM</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>64.7</v>
+        <v>65.7</v>
       </c>
       <c r="D21" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1961,26 +1961,28 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0.1144958764235571</v>
-      </c>
-      <c r="G21" t="inlineStr"/>
+        <v>0.1701360960301399</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.365979383233586</v>
+      </c>
       <c r="H21" t="n">
-        <v>0.5150299699999999</v>
+        <v>0.62473</v>
       </c>
       <c r="I21" t="n">
-        <v>0.03808</v>
+        <v>0.103310004</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1588559589226195</v>
+        <v>0.01927658652804842</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.723268174038375</v>
+        <v>-0.4140134286333117</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2196363183459956</v>
+        <v>0.04656029296364089</v>
       </c>
       <c r="M21" t="n">
-        <v>199272824832</v>
+        <v>34845491200</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -1989,43 +1991,43 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="Q21" t="b">
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0.2163148817331868</v>
+        <v>0.2842836492104213</v>
       </c>
       <c r="S21" t="n">
-        <v>1.840162774049261</v>
+        <v>0.2635467162598177</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-08-16 07:35:03</t>
+          <t>2026-08-23 07:36:41</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Axon Enterprise, Inc.</t>
+          <t>Datadog, Inc.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>AXON</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>64.59999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -2033,28 +2035,26 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0.3278726393918761</v>
-      </c>
-      <c r="G22" t="n">
-        <v>-0.09393302099393697</v>
-      </c>
+        <v>0.2694953937625746</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>0.5952499999999999</v>
+        <v>0.79536</v>
       </c>
       <c r="I22" t="n">
-        <v>0.00509</v>
+        <v>0.0018000001</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1314789419578022</v>
+        <v>0.2103395297512944</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.4468123296835991</v>
+        <v>-0.5840336134453781</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2942598787524648</v>
+        <v>0.3601496984230798</v>
       </c>
       <c r="M22" t="n">
-        <v>49784725504</v>
+        <v>84605255680</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -2067,39 +2067,39 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="Q22" t="b">
         <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>0.578685729245036</v>
+        <v>0.08062741869554424</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4061862291432403</v>
+        <v>1.037177828608157</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-08-16 07:35:03</t>
+          <t>2026-08-23 07:36:41</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Garmin Ltd.</t>
+          <t>Incyte Corporation</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GRMN</t>
+          <t>INCY</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>64.3</v>
+        <v>65.5</v>
       </c>
       <c r="D23" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -2107,28 +2107,28 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0.142358869424539</v>
+        <v>0.1483959547833886</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1945038186480894</v>
+        <v>0.6156160063417289</v>
       </c>
       <c r="H23" t="n">
-        <v>0.60081</v>
+        <v>0.55659</v>
       </c>
       <c r="I23" t="n">
-        <v>0.12174</v>
+        <v>0.16832</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.06419825918762079</v>
+        <v>-0.005359518034582567</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.39822695035461</v>
+        <v>-0.3655426023002895</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.1612102323322267</v>
+        <v>-0.01466181506849311</v>
       </c>
       <c r="M23" t="n">
-        <v>59823996928</v>
+        <v>25906798592</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -2147,33 +2147,33 @@
         <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>0.3290706526187623</v>
+        <v>0.3120828739718997</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5390618576759405</v>
+        <v>0.2614488545554421</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-08-16 07:35:03</t>
+          <t>2026-08-23 07:36:41</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>KLA Corporation</t>
+          <t>Visa Inc.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>64.3</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="D24" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -2181,37 +2181,37 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0.08964649002419045</v>
+        <v>0.1092124213025429</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1486507049039818</v>
+        <v>0.1337066930484769</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6130100000000001</v>
+        <v>0.97725</v>
       </c>
       <c r="I24" t="n">
-        <v>0.20799999</v>
+        <v>0.1911</v>
       </c>
       <c r="J24" t="n">
-        <v>0.1377272236402907</v>
+        <v>0.1228053040103492</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.591478499901826</v>
+        <v>-0.2079290642518328</v>
       </c>
       <c r="L24" t="n">
-        <v>0.2328524598326917</v>
+        <v>0.5906115359688909</v>
       </c>
       <c r="M24" t="n">
-        <v>266169712640</v>
+        <v>692749271040</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P24" t="n">
@@ -2221,30 +2221,30 @@
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0.07758302643336323</v>
+        <v>0.12264223679714</v>
       </c>
       <c r="S24" t="n">
-        <v>0.4077612800205148</v>
+        <v>0.1606167280358461</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-08-16 07:35:03</t>
+          <t>2026-08-23 07:36:41</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Lam Research Corporation</t>
+          <t>News Corporation</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>NWSA</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>64</v>
+        <v>64.5</v>
       </c>
       <c r="D25" t="n">
         <v>64</v>
@@ -2255,37 +2255,37 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0.1005582390165327</v>
+        <v>0.0405993172034298</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2014836612049711</v>
+        <v>0.5822968332827563</v>
       </c>
       <c r="H25" t="n">
-        <v>0.50469</v>
+        <v>0.57167</v>
       </c>
       <c r="I25" t="n">
-        <v>0.22840999</v>
+        <v>0.04658</v>
       </c>
       <c r="J25" t="n">
-        <v>0.1100478396919002</v>
+        <v>0.1903390388413431</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.7168431820917078</v>
+        <v>-0.2692560895325872</v>
       </c>
       <c r="L25" t="n">
-        <v>0.1535173137460649</v>
+        <v>0.7069070904645481</v>
       </c>
       <c r="M25" t="n">
-        <v>415889031168</v>
+        <v>16407464960</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
+          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P25" t="n">
@@ -2295,33 +2295,33 @@
         <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0.111797107429453</v>
+        <v>0.1568925702960742</v>
       </c>
       <c r="S25" t="n">
-        <v>0.4397189508246566</v>
+        <v>0.2899346288990008</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-08-16 07:35:03</t>
+          <t>2026-08-23 07:36:41</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Lam Research Corporation</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>63.1</v>
+        <v>63.5</v>
       </c>
       <c r="D26" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -2329,37 +2329,37 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0.1631543559703441</v>
+        <v>0.1005582390165327</v>
       </c>
       <c r="G26" t="n">
-        <v>4.460320482827598</v>
+        <v>0.2014836612049711</v>
       </c>
       <c r="H26" t="n">
-        <v>0.31051</v>
+        <v>0.50469</v>
       </c>
       <c r="I26" t="n">
-        <v>0.05065</v>
+        <v>0.22840999</v>
       </c>
       <c r="J26" t="n">
-        <v>0.09914965524729902</v>
+        <v>0.1826586942675159</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.2838916336391769</v>
+        <v>-0.7002866242038217</v>
       </c>
       <c r="L26" t="n">
-        <v>0.3492517689806848</v>
+        <v>0.2608341898221838</v>
       </c>
       <c r="M26" t="n">
-        <v>382217289728</v>
+        <v>392914796544</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P26" t="n">
@@ -2369,30 +2369,30 @@
         <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>0.2651408771769854</v>
+        <v>0.03964138812961071</v>
       </c>
       <c r="S26" t="n">
-        <v>0.1805314754252272</v>
+        <v>0.2844915016830847</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-08-16 07:35:03</t>
+          <t>2026-08-23 07:36:41</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>United Airlines Holdings, Inc.</t>
+          <t>Axon Enterprise, Inc.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>UAL</t>
+          <t>AXON</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>62.9</v>
+        <v>63.4</v>
       </c>
       <c r="D27" t="n">
         <v>63</v>
@@ -2403,37 +2403,37 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>0.09529134601036815</v>
+        <v>0.3278726393918761</v>
       </c>
       <c r="G27" t="n">
-        <v>0.6599631084110487</v>
+        <v>-0.09393302099393697</v>
       </c>
       <c r="H27" t="n">
-        <v>0.31816</v>
+        <v>0.5952499999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>0.03381</v>
+        <v>0.00509</v>
       </c>
       <c r="J27" t="n">
-        <v>0.2936985798627731</v>
+        <v>0.104586602947033</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.324716770384554</v>
+        <v>-0.4599601752289925</v>
       </c>
       <c r="L27" t="n">
-        <v>0.9044761670761666</v>
+        <v>0.2273818660386506</v>
       </c>
       <c r="M27" t="n">
-        <v>40681570304</v>
+        <v>50996789248</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Stærk eps-vækst, positivt momentum, analytiker-upside over 20 %</t>
+          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P27" t="n">
@@ -2443,33 +2443,33 @@
         <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>0.3053530589447424</v>
+        <v>0.6102760257977811</v>
       </c>
       <c r="S27" t="n">
-        <v>0.1467519930309358</v>
+        <v>0.4467285720585414</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-08-16 07:35:03</t>
+          <t>2026-08-23 07:36:41</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Corpay, Inc.</t>
+          <t>F5, Inc.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CPAY</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>62.4</v>
+        <v>63.3</v>
       </c>
       <c r="D28" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -2477,28 +2477,28 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>0.097332408585459</v>
+        <v>0.04631913174341684</v>
       </c>
       <c r="G28" t="n">
-        <v>0.06564477917470324</v>
+        <v>0.3082491584064506</v>
       </c>
       <c r="H28" t="n">
-        <v>0.8053900000000001</v>
+        <v>0.81865996</v>
       </c>
       <c r="I28" t="n">
-        <v>0.06315999999999999</v>
+        <v>0.07976999999999999</v>
       </c>
       <c r="J28" t="n">
-        <v>0.07912559865900382</v>
+        <v>0.1338169149572317</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.3945402298850575</v>
+        <v>-0.4182461066479474</v>
       </c>
       <c r="L28" t="n">
-        <v>0.2005514081087642</v>
+        <v>0.3199477839249085</v>
       </c>
       <c r="M28" t="n">
-        <v>27419449344</v>
+        <v>21780514816</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Høj bruttomargin, positivt momentum</t>
+          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P28" t="n">
@@ -2517,33 +2517,33 @@
         <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>0.2686453475969344</v>
+        <v>0.002423749403686282</v>
       </c>
       <c r="S28" t="n">
-        <v>0.2996389785406306</v>
+        <v>0.381622847962199</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-08-16 07:35:03</t>
+          <t>2026-08-23 07:36:41</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Incyte Corporation</t>
+          <t>Hewlett Packard Enterprise Comp</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>INCY</t>
+          <t>HPE</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>62.2</v>
+        <v>63.1</v>
       </c>
       <c r="D29" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -2551,73 +2551,71 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>0.1483959547833886</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0.6156160063417289</v>
-      </c>
+        <v>0.06370170685761956</v>
+      </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
-        <v>0.55659</v>
+        <v>0.33776</v>
       </c>
       <c r="I29" t="n">
-        <v>0.16832</v>
+        <v>0.01966</v>
       </c>
       <c r="J29" t="n">
-        <v>0.04172694740346206</v>
+        <v>0.2206095416276894</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.3251498002663116</v>
+        <v>-0.6288119738072966</v>
       </c>
       <c r="L29" t="n">
-        <v>0.1283314563603788</v>
+        <v>0.3508354656352276</v>
       </c>
       <c r="M29" t="n">
-        <v>24356161536</v>
+        <v>70778675200</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
+          <t>Positivt momentum, analytiker-upside over 20 %</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="Q29" t="b">
         <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>0.2307693029040072</v>
+        <v>0.5780504794710699</v>
       </c>
       <c r="S29" t="n">
-        <v>0.1926551231971154</v>
+        <v>1.524662337871772</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2026-08-16 07:35:03</t>
+          <t>2026-08-23 07:36:41</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Delta Air Lines, Inc.</t>
+          <t>CrowdStrike Holdings, Inc.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>62</v>
+        <v>62.6</v>
       </c>
       <c r="D30" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -2625,28 +2623,26 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>0.07799197884220499</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.5492464741024845</v>
-      </c>
+        <v>0.2900686653697968</v>
+      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
-        <v>0.187</v>
+        <v>0.75136</v>
       </c>
       <c r="I30" t="n">
-        <v>0.04019</v>
+        <v>-0.0100300005</v>
       </c>
       <c r="J30" t="n">
-        <v>0.1809829882484613</v>
+        <v>0.09265433706694459</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.3841074426412983</v>
+        <v>-0.5536337587913518</v>
       </c>
       <c r="L30" t="n">
-        <v>0.4711780303030307</v>
+        <v>0.1673567328502872</v>
       </c>
       <c r="M30" t="n">
-        <v>58758619136</v>
+        <v>195454861312</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2655,43 +2651,43 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Stærk eps-vækst, positivt momentum</t>
+          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="Q30" t="b">
         <v>1</v>
       </c>
       <c r="R30" t="n">
-        <v>0.2518604017507877</v>
+        <v>0.1844561512532248</v>
       </c>
       <c r="S30" t="n">
-        <v>0.2957160641454124</v>
+        <v>0.9758105397158472</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2026-08-16 07:35:03</t>
+          <t>2026-08-23 07:36:41</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>F5, Inc.</t>
+          <t>Marvell Technology, Inc.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>61.9</v>
+        <v>62.4</v>
       </c>
       <c r="D31" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -2699,28 +2695,26 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>0.04631913174341684</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0.3082491584064506</v>
-      </c>
+        <v>0.1144958764235571</v>
+      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
-        <v>0.81865996</v>
+        <v>0.5150299699999999</v>
       </c>
       <c r="I31" t="n">
-        <v>0.07976999999999999</v>
+        <v>0.03808</v>
       </c>
       <c r="J31" t="n">
-        <v>0.08159722222222232</v>
+        <v>0.1134859095511307</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.4450396825396825</v>
+        <v>-0.7408032399595005</v>
       </c>
       <c r="L31" t="n">
-        <v>0.1833481943825236</v>
+        <v>0.1531930523917997</v>
       </c>
       <c r="M31" t="n">
-        <v>22832080896</v>
+        <v>212753924096</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2729,24 +2723,24 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="Q31" t="b">
         <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>0.1058998224223302</v>
+        <v>0.243371246531729</v>
       </c>
       <c r="S31" t="n">
-        <v>0.5388139421149001</v>
+        <v>1.984614243681185</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2026-08-16 07:35:03</t>
+          <t>2026-08-23 07:36:41</t>
         </is>
       </c>
     </row>

--- a/data/compounder_radar.xlsx
+++ b/data/compounder_radar.xlsx
@@ -429,13 +429,13 @@
     <col width="15" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="23" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
     <col width="17" customWidth="1" min="13" max="13"/>
     <col width="8" customWidth="1" min="14" max="14"/>
     <col width="45" customWidth="1" min="15" max="15"/>
     <col width="19" customWidth="1" min="16" max="16"/>
     <col width="18" customWidth="1" min="17" max="17"/>
-    <col width="23" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
     <col width="21" customWidth="1" min="19" max="19"/>
     <col width="21" customWidth="1" min="20" max="20"/>
   </cols>
@@ -554,10 +554,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>84.3</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -577,16 +577,16 @@
         <v>0.14119</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2818191889742909</v>
+        <v>0.2376660354181594</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.3929499072356215</v>
+        <v>-0.4138601699252739</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7171885876163494</v>
+        <v>0.5742665100173138</v>
       </c>
       <c r="M2" t="n">
-        <v>237930037248</v>
+        <v>246418096128</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -605,14 +605,14 @@
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2696009054842301</v>
+        <v>0.2251834413195413</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4206642325072321</v>
+        <v>0.4635206358263109</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-08-23 07:36:41</t>
+          <t>2026-08-30 12:41:47</t>
         </is>
       </c>
     </row>
@@ -628,10 +628,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>82.09999999999999</v>
+        <v>80</v>
       </c>
       <c r="D3" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -651,16 +651,16 @@
         <v>0.2038</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1344602614254367</v>
+        <v>0.1598502164081117</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.2837515504245779</v>
+        <v>-0.2698536205806547</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4738661735036991</v>
+        <v>0.5923589836006488</v>
       </c>
       <c r="M3" t="n">
-        <v>162430025728</v>
+        <v>154506379264</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -679,33 +679,33 @@
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3160507220066857</v>
+        <v>0.2312425829203129</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2916188965059978</v>
+        <v>0.2184486889498227</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-08-23 07:36:41</t>
+          <t>2026-08-30 12:41:47</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sandisk Corporation</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>75.2</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -713,100 +713,102 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.4928519097558826</v>
-      </c>
-      <c r="G4" t="inlineStr"/>
+        <v>1.000450949944396</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.04239508347386</v>
+      </c>
       <c r="H4" t="n">
-        <v>0.71474</v>
+        <v>0.74674004</v>
       </c>
       <c r="I4" t="n">
-        <v>0.43910998</v>
+        <v>0.53572</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3321223246955041</v>
+        <v>0.4866420592967131</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.9711731241541778</v>
+        <v>-0.2458285451620318</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3419805557168387</v>
+        <v>1.979599476439789</v>
       </c>
       <c r="M4" t="n">
-        <v>233696444416</v>
+        <v>5253179637760</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="Q4" t="b">
         <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>0.03491023845914576</v>
+        <v>0.03155986221998819</v>
       </c>
       <c r="S4" t="n">
-        <v>1.455621071736712</v>
+        <v>0.2292755810438503</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-08-23 07:36:41</t>
+          <t>2026-08-30 12:41:47</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Micron Technology, Inc.</t>
+          <t>Veeva Systems Inc.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>74.5</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>High Conviction</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.06713489726936261</v>
+        <v>0.1402968452680178</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.006929629272242499</v>
+        <v>0.2194365698361114</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7256899999999999</v>
+        <v>0.74961</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3487</v>
+        <v>0.07583000500000001</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5671751587744884</v>
+        <v>0.06282868914669848</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.8818241999213885</v>
+        <v>-0.4649246449094654</v>
       </c>
       <c r="L5" t="n">
-        <v>0.643183934876192</v>
+        <v>0.1351373600746269</v>
       </c>
       <c r="M5" t="n">
-        <v>1091874717696</v>
+        <v>44798558208</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -815,7 +817,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Høj bruttomargin, positivt momentum, analytiker-upside over 20 %</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -825,33 +827,33 @@
         <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2687688546422129</v>
+        <v>0.5870712874465693</v>
       </c>
       <c r="S5" t="n">
-        <v>1.259231023662006</v>
+        <v>0.5201912575796177</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-08-23 07:36:41</t>
+          <t>2026-08-30 12:41:47</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Robinhood Markets, Inc.</t>
+          <t>Expedia Group, Inc.</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>EXPE</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>74.2</v>
+        <v>73.2</v>
       </c>
       <c r="D6" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -859,26 +861,28 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.4878747583673768</v>
-      </c>
-      <c r="G6" t="inlineStr"/>
+        <v>0.08087962506974211</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.6534957812135467</v>
+      </c>
       <c r="H6" t="n">
-        <v>0.9189000000000001</v>
+        <v>0.90433</v>
       </c>
       <c r="I6" t="n">
-        <v>0.04528</v>
+        <v>0.061079998</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1091350226579118</v>
+        <v>0.02971278533268595</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.4126051974475169</v>
+        <v>-0.4374089363768819</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2645022974335985</v>
+        <v>0.06792907702984081</v>
       </c>
       <c r="M6" t="n">
-        <v>97217765376</v>
+        <v>39540072448</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -887,43 +891,43 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="Q6" t="b">
         <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4242623796275062</v>
+        <v>0.4611582834734427</v>
       </c>
       <c r="S6" t="n">
-        <v>0.420706824153033</v>
+        <v>0.5361519933949572</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-08-23 07:36:41</t>
+          <t>2026-08-30 12:41:47</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Expedia Group, Inc.</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>EXPE</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>73</v>
+        <v>72.2</v>
       </c>
       <c r="D7" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -931,37 +935,37 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.08087962506974211</v>
+        <v>0.1612397915820203</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6534957812135467</v>
+        <v>0.2285599828574523</v>
       </c>
       <c r="H7" t="n">
-        <v>0.90433</v>
+        <v>0.67944</v>
       </c>
       <c r="I7" t="n">
-        <v>0.061079998</v>
+        <v>0.14088</v>
       </c>
       <c r="J7" t="n">
-        <v>0.04538936044523223</v>
+        <v>0.1089005510875705</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.4237477847215745</v>
+        <v>-0.3200007789223609</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1071140949446037</v>
+        <v>0.3403133937808073</v>
       </c>
       <c r="M7" t="n">
-        <v>38601822208</v>
+        <v>3813240733696</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -971,30 +975,30 @@
         <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4776859946775289</v>
+        <v>0.1427166697123534</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5874392660754975</v>
+        <v>0.3128561087687154</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-08-23 07:36:41</t>
+          <t>2026-08-30 12:41:47</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Eli Lilly and Company</t>
+          <t>Mastercard Incorporated</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>72.40000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="D8" t="n">
         <v>72</v>
@@ -1005,32 +1009,32 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.3168737488062043</v>
+        <v>0.1382198495222513</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5171329563234539</v>
+        <v>0.173598959321368</v>
       </c>
       <c r="H8" t="n">
-        <v>0.83399004</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.20357001</v>
+        <v>0.24063</v>
       </c>
       <c r="J8" t="n">
-        <v>0.04750724868567779</v>
+        <v>0.1245750041995635</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.4470049386649674</v>
+        <v>-0.2196875524945405</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1062790241816204</v>
+        <v>0.5670553601468126</v>
       </c>
       <c r="M8" t="n">
-        <v>1119009636352</v>
+        <v>521488695296</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1045,33 +1049,33 @@
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2069302535023232</v>
+        <v>0.2071296354970109</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2474871155709406</v>
+        <v>0.1548937127565413</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-08-23 07:36:41</t>
+          <t>2026-08-30 12:41:47</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc.</t>
+          <t>Robinhood Markets, Inc.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>72.3</v>
+        <v>70.3</v>
       </c>
       <c r="D9" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1079,26 +1083,26 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.3291712528765784</v>
+        <v>0.4878747583673768</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>0.84796</v>
+        <v>0.9189000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>0.17292999</v>
+        <v>0.04528</v>
       </c>
       <c r="J9" t="n">
-        <v>0.06524397021229311</v>
+        <v>0.1654074429311336</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.4088585083916861</v>
+        <v>-0.3908018415499712</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1595759140954196</v>
+        <v>0.4232514418947108</v>
       </c>
       <c r="M9" t="n">
-        <v>432406331392</v>
+        <v>93738319872</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -1117,14 +1121,14 @@
         <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3094641140557755</v>
+        <v>0.1056203474246546</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3305234777626627</v>
+        <v>0.3745550986636137</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-08-23 07:36:41</t>
+          <t>2026-08-30 12:41:47</t>
         </is>
       </c>
     </row>
@@ -1140,10 +1144,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>72.2</v>
+        <v>69.2</v>
       </c>
       <c r="D10" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1163,16 +1167,16 @@
         <v>0.14166</v>
       </c>
       <c r="J10" t="n">
-        <v>0.04791121099602624</v>
+        <v>-0.03093463855421696</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5208781186893362</v>
+        <v>-0.5569277108433734</v>
       </c>
       <c r="L10" t="n">
-        <v>0.09198161580790382</v>
+        <v>-0.05554515954570056</v>
       </c>
       <c r="M10" t="n">
-        <v>112632381440</v>
+        <v>121796468736</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1191,33 +1195,33 @@
         <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1857715629980159</v>
+        <v>0.2031600966246192</v>
       </c>
       <c r="S10" t="n">
-        <v>0.9188749313354492</v>
+        <v>1.100468209085766</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-08-23 07:36:41</t>
+          <t>2026-08-30 12:41:47</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ServiceNow, Inc.</t>
+          <t>Interactive Brokers Group, Inc.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NOW</t>
+          <t>IBKR</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>72</v>
+        <v>69.2</v>
       </c>
       <c r="D11" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1225,28 +1229,28 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.2237651786474262</v>
+        <v>0.3459787421885367</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7345580184539504</v>
+        <v>0.3328887406583814</v>
       </c>
       <c r="H11" t="n">
-        <v>0.74768996</v>
+        <v>0.93036</v>
       </c>
       <c r="I11" t="n">
-        <v>0.04249</v>
+        <v>0.022839999</v>
       </c>
       <c r="J11" t="n">
-        <v>0.107034090909091</v>
+        <v>0.1074011894824707</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.3676836861768369</v>
+        <v>-0.3849123539232053</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2911037256562238</v>
+        <v>0.279027649769585</v>
       </c>
       <c r="M11" t="n">
-        <v>132830584832</v>
+        <v>163293675520</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1265,33 +1269,33 @@
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>0.288795190902462</v>
+        <v>0.1031052710980649</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2321856705083392</v>
+        <v>0.3476200478588702</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-08-23 07:36:41</t>
+          <t>2026-08-30 12:41:47</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>Salesforce, Inc.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>71.7</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1299,37 +1303,37 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.1612397915820203</v>
+        <v>0.09820006113830493</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2285599828574523</v>
+        <v>2.336504917866317</v>
       </c>
       <c r="H12" t="n">
-        <v>0.67944</v>
+        <v>0.77282</v>
       </c>
       <c r="I12" t="n">
-        <v>0.14088</v>
+        <v>0.05704</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1784076235410976</v>
+        <v>0.02555214843750009</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.27737770052148</v>
+        <v>-0.4284375</v>
       </c>
       <c r="L12" t="n">
-        <v>0.6431938227394808</v>
+        <v>0.05964031728665228</v>
       </c>
       <c r="M12" t="n">
-        <v>3588320657408</v>
+        <v>210688000000</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
+          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -1339,33 +1343,33 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0.155240445038888</v>
+        <v>0.3430702605548377</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2214543204099817</v>
+        <v>0.3209232029688069</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-08-23 07:36:41</t>
+          <t>2026-08-30 12:41:47</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices, Inc.</t>
+          <t>Blackstone Inc.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>71.09999999999999</v>
+        <v>67.8</v>
       </c>
       <c r="D13" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1373,32 +1377,32 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.1364359933536843</v>
+        <v>0.2027465724146367</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4666355102918431</v>
+        <v>0.1792330812083591</v>
       </c>
       <c r="H13" t="n">
-        <v>0.55724</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>0.05128</v>
+        <v>0.1433</v>
       </c>
       <c r="J13" t="n">
-        <v>0.295492234548336</v>
+        <v>0.01164140740220532</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.6846909667194929</v>
+        <v>-0.2855537607978087</v>
       </c>
       <c r="L13" t="n">
-        <v>0.4315702249791685</v>
+        <v>0.0407678307919335</v>
       </c>
       <c r="M13" t="n">
-        <v>772568776704</v>
+        <v>170198450176</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1413,33 +1417,33 @@
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0.05262573423526007</v>
+        <v>0.2297383676281706</v>
       </c>
       <c r="S13" t="n">
-        <v>1.364476714622136</v>
+        <v>0.2805445058422442</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-08-23 07:36:41</t>
+          <t>2026-08-30 12:41:47</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Seagate Technology Holdings PLC</t>
+          <t>Incyte Corporation</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>STX</t>
+          <t>INCY</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>69.40000000000001</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1447,71 +1451,73 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.1820341908356484</v>
-      </c>
-      <c r="G14" t="inlineStr"/>
+        <v>0.1483959547833886</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.6156160063417289</v>
+      </c>
       <c r="H14" t="n">
-        <v>0.45576</v>
+        <v>0.55659</v>
       </c>
       <c r="I14" t="n">
-        <v>0.29354998</v>
+        <v>0.16832</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3235294117647058</v>
+        <v>0.02215164428720739</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.8133176470588235</v>
+        <v>-0.3479938892015759</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3977897355783139</v>
+        <v>0.06365526802218077</v>
       </c>
       <c r="M14" t="n">
-        <v>192949993472</v>
+        <v>25209518080</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="Q14" t="b">
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0.0495348748175839</v>
+        <v>0.2856109726374132</v>
       </c>
       <c r="S14" t="n">
-        <v>1.072656535508107</v>
+        <v>0.2281031585784812</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-08-23 07:36:41</t>
+          <t>2026-08-30 12:41:47</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Veeva Systems Inc.</t>
+          <t>Visa Inc.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>69.09999999999999</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1519,32 +1525,32 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0.1402968452680178</v>
+        <v>0.1092124213025429</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2194365698361114</v>
+        <v>0.1337066930484769</v>
       </c>
       <c r="H15" t="n">
-        <v>0.75021005</v>
+        <v>0.97725</v>
       </c>
       <c r="I15" t="n">
-        <v>0.07298</v>
+        <v>0.1911</v>
       </c>
       <c r="J15" t="n">
-        <v>0.02287789431222254</v>
+        <v>0.09513144654088035</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.4027833803953207</v>
+        <v>-0.2298480083857443</v>
       </c>
       <c r="L15" t="n">
-        <v>0.05679949924887297</v>
+        <v>0.4138884961805944</v>
       </c>
       <c r="M15" t="n">
-        <v>40269692928</v>
+        <v>712465252352</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1559,33 +1565,33 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0.5663106539741156</v>
+        <v>0.171433177938783</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3748544021577422</v>
+        <v>0.1966684830677541</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-08-23 07:36:41</t>
+          <t>2026-08-30 12:41:47</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Interactive Brokers Group, Inc.</t>
+          <t>DexCom, Inc.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>IBKR</t>
+          <t>DXCM</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>68.90000000000001</v>
+        <v>67.5</v>
       </c>
       <c r="D16" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1593,28 +1599,28 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0.3459787421885367</v>
+        <v>0.1701360960301399</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3328887406583814</v>
+        <v>0.365979383233586</v>
       </c>
       <c r="H16" t="n">
-        <v>0.93036</v>
+        <v>0.62473</v>
       </c>
       <c r="I16" t="n">
-        <v>0.022839999</v>
+        <v>0.103310004</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1306416320443167</v>
+        <v>0.03633560889671883</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.3720038350910834</v>
+        <v>-0.4042061219995595</v>
       </c>
       <c r="L16" t="n">
-        <v>0.351183562428408</v>
+        <v>0.08989376191773371</v>
       </c>
       <c r="M16" t="n">
-        <v>159937167360</v>
+        <v>34271905792</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1633,33 +1639,33 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0.1209003878050932</v>
+        <v>0.2316246586094162</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2643279441332309</v>
+        <v>0.2368241770036148</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-08-23 07:36:41</t>
+          <t>2026-08-30 12:41:47</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc.</t>
+          <t>Palantir Technologies Inc.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>67.7</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1667,28 +1673,26 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0.03534983888485344</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.388859258627138</v>
-      </c>
+        <v>0.3291712528765784</v>
+      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>0.19212</v>
+        <v>0.84796</v>
       </c>
       <c r="I17" t="n">
-        <v>0.07004000000000001</v>
+        <v>0.17292999</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1508835957292798</v>
+        <v>0.0289333834344303</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.7506786102062974</v>
+        <v>-0.4290085350797144</v>
       </c>
       <c r="L17" t="n">
-        <v>0.200996263484602</v>
+        <v>0.06744244244244271</v>
       </c>
       <c r="M17" t="n">
-        <v>285646618624</v>
+        <v>447665733632</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1697,40 +1701,40 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Stærk eps-vækst, positivt momentum</t>
+          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="Q17" t="b">
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0.7516238195631495</v>
+        <v>0.1900472804136464</v>
       </c>
       <c r="S17" t="n">
-        <v>2.632785198046367</v>
+        <v>0.3578977328591939</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-08-23 07:36:41</t>
+          <t>2026-08-30 12:41:47</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Amphenol Corporation</t>
+          <t>News Corporation</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>APH</t>
+          <t>NWSA</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>67.40000000000001</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="D18" t="n">
         <v>67</v>
@@ -1741,28 +1745,28 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0.2230660589034148</v>
+        <v>0.0405993172034298</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2972340671812952</v>
+        <v>0.5822968332827563</v>
       </c>
       <c r="H18" t="n">
-        <v>0.38952</v>
+        <v>0.57167</v>
       </c>
       <c r="I18" t="n">
-        <v>0.14473</v>
+        <v>0.04658</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2236013629705116</v>
+        <v>0.1676622537939942</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.3283867269600662</v>
+        <v>-0.2831772683241847</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6809086501163698</v>
+        <v>0.5920752565564427</v>
       </c>
       <c r="M18" t="n">
-        <v>193590722560</v>
+        <v>16635842560</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1771,7 +1775,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, positivt momentum</t>
+          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -1781,33 +1785,33 @@
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2593854585494386</v>
+        <v>0.1865899946630778</v>
       </c>
       <c r="S18" t="n">
-        <v>0.04315191881713076</v>
+        <v>0.2803382915574564</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-08-23 07:36:41</t>
+          <t>2026-08-30 12:41:47</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Salesforce, Inc.</t>
+          <t>DoorDash, Inc.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>DASH</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>66.8</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="D19" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1815,73 +1819,71 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0.09820006113830493</v>
-      </c>
-      <c r="G19" t="n">
-        <v>2.336504917866317</v>
-      </c>
+        <v>0.2772574009717286</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>0.77643996</v>
+        <v>0.52225</v>
       </c>
       <c r="I19" t="n">
-        <v>0.05703</v>
+        <v>0.029719999</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1664399770521585</v>
+        <v>0.06571605981245243</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.3004732992302911</v>
+        <v>-0.3946946016727211</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5539260143198091</v>
+        <v>0.1664985017123287</v>
       </c>
       <c r="M19" t="n">
-        <v>171310235648</v>
+        <v>102578962432</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="Q19" t="b">
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>0.1894382314755338</v>
+        <v>0.4862201988288599</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1354198866051552</v>
+        <v>0.3415311602853335</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-08-23 07:36:41</t>
+          <t>2026-08-30 12:41:47</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DoorDash, Inc.</t>
+          <t>F5, Inc.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DASH</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>66.59999999999999</v>
+        <v>63.5</v>
       </c>
       <c r="D20" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1889,26 +1891,28 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0.2772574009717286</v>
-      </c>
-      <c r="G20" t="inlineStr"/>
+        <v>0.04631913174341684</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.3082491584064506</v>
+      </c>
       <c r="H20" t="n">
-        <v>0.52225</v>
+        <v>0.81865996</v>
       </c>
       <c r="I20" t="n">
-        <v>0.029719999</v>
+        <v>0.07976999999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1288989216519754</v>
+        <v>0.1061789772727273</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.3588080003579578</v>
+        <v>-0.432426948051948</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3592420501309387</v>
+        <v>0.2455419990614735</v>
       </c>
       <c r="M20" t="n">
-        <v>96837246976</v>
+        <v>22324701184</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -1917,43 +1921,43 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="Q20" t="b">
         <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4032146637658329</v>
+        <v>0.0281392037654129</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2677407340439446</v>
+        <v>0.4528302311175849</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-08-23 07:36:41</t>
+          <t>2026-08-30 12:41:47</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DexCom, Inc.</t>
+          <t>Marvell Technology, Inc.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DXCM</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>65.7</v>
+        <v>63.5</v>
       </c>
       <c r="D21" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1961,28 +1965,26 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0.1701360960301399</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.365979383233586</v>
-      </c>
+        <v>0.1144958764235571</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>0.62473</v>
+        <v>0.52216</v>
       </c>
       <c r="I21" t="n">
-        <v>0.103310004</v>
+        <v>0.04125</v>
       </c>
       <c r="J21" t="n">
-        <v>0.01927658652804842</v>
+        <v>0.2874706859939065</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.4140134286333117</v>
+        <v>-0.7163696796233034</v>
       </c>
       <c r="L21" t="n">
-        <v>0.04656029296364089</v>
+        <v>0.401288181466684</v>
       </c>
       <c r="M21" t="n">
-        <v>34845491200</v>
+        <v>194677391360</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -1991,43 +1993,43 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
+          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="Q21" t="b">
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0.2842836492104213</v>
+        <v>0.05694362072151526</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2635467162598177</v>
+        <v>1.653714013332679</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-08-23 07:36:41</t>
+          <t>2026-08-30 12:41:47</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Datadog, Inc.</t>
+          <t>Workday, Inc.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>65.59999999999999</v>
+        <v>63.3</v>
       </c>
       <c r="D22" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -2035,26 +2037,26 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0.2694953937625746</v>
+        <v>0.1539697807235301</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>0.79536</v>
+        <v>0.75795</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0018000001</v>
+        <v>0.04513</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2103395297512944</v>
+        <v>0.003669939429464586</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.5840336134453781</v>
+        <v>-0.4609222352481438</v>
       </c>
       <c r="L22" t="n">
-        <v>0.3601496984230798</v>
+        <v>0.007962166172106719</v>
       </c>
       <c r="M22" t="n">
-        <v>84605255680</v>
+        <v>49337520128</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -2073,33 +2075,33 @@
         <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>0.08062741869554424</v>
+        <v>0.4003693672743183</v>
       </c>
       <c r="S22" t="n">
-        <v>1.037177828608157</v>
+        <v>0.5305024643241945</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-08-23 07:36:41</t>
+          <t>2026-08-30 12:41:47</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Incyte Corporation</t>
+          <t>KKR &amp; Co. Inc.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>INCY</t>
+          <t>KKR</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>65.5</v>
+        <v>62.3</v>
       </c>
       <c r="D23" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -2107,73 +2109,71 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0.1483959547833886</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.6156160063417289</v>
-      </c>
+        <v>0.5112422937117458</v>
+      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>0.55659</v>
+        <v>0.54767</v>
       </c>
       <c r="I23" t="n">
-        <v>0.16832</v>
+        <v>0.01386</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.005359518034582567</v>
+        <v>0.1775487670224511</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.3655426023002895</v>
+        <v>-0.2393264630106736</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.01466181506849311</v>
+        <v>0.741868512110726</v>
       </c>
       <c r="M23" t="n">
-        <v>25906798592</v>
+        <v>100375822336</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
+          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="Q23" t="b">
         <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>0.3120828739718997</v>
+        <v>0.1349439420001135</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2614488545554421</v>
+        <v>0.2442996153695307</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-08-23 07:36:41</t>
+          <t>2026-08-30 12:41:47</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Visa Inc.</t>
+          <t>ServiceNow, Inc.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>NOW</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>65.09999999999999</v>
+        <v>61.7</v>
       </c>
       <c r="D24" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -2181,32 +2181,32 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0.1092124213025429</v>
+        <v>0.2237651786474262</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1337066930484769</v>
+        <v>0.7345580184539504</v>
       </c>
       <c r="H24" t="n">
-        <v>0.97725</v>
+        <v>0.74768996</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1911</v>
+        <v>0.04249</v>
       </c>
       <c r="J24" t="n">
-        <v>0.1228053040103492</v>
+        <v>-0.01712569967521249</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.2079290642518328</v>
+        <v>-0.4386013406122591</v>
       </c>
       <c r="L24" t="n">
-        <v>0.5906115359688909</v>
+        <v>-0.03904616354183077</v>
       </c>
       <c r="M24" t="n">
-        <v>692749271040</v>
+        <v>149610184704</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2221,33 +2221,33 @@
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0.12264223679714</v>
+        <v>0.1635442913733003</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1606167280358461</v>
+        <v>0.3397833890545421</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-08-23 07:36:41</t>
+          <t>2026-08-30 12:41:47</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>News Corporation</t>
+          <t>CrowdStrike Holdings, Inc.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NWSA</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>64.5</v>
+        <v>61</v>
       </c>
       <c r="D25" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -2255,73 +2255,71 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0.0405993172034298</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.5822968332827563</v>
-      </c>
+        <v>0.2900686653697968</v>
+      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>0.57167</v>
+        <v>0.75185996</v>
       </c>
       <c r="I25" t="n">
-        <v>0.04658</v>
+        <v>-0.0078100003</v>
       </c>
       <c r="J25" t="n">
-        <v>0.1903390388413431</v>
+        <v>0.04204043040293026</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.2692560895325872</v>
+        <v>-0.6076923076923078</v>
       </c>
       <c r="L25" t="n">
-        <v>0.7069070904645481</v>
+        <v>0.06918045509342954</v>
       </c>
       <c r="M25" t="n">
-        <v>16407464960</v>
+        <v>223627362304</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="Q25" t="b">
         <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0.1568925702960742</v>
+        <v>0.1950752059999146</v>
       </c>
       <c r="S25" t="n">
-        <v>0.2899346288990008</v>
+        <v>1.348513225937955</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-08-23 07:36:41</t>
+          <t>2026-08-30 12:41:47</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Lam Research Corporation</t>
+          <t>Zebra Technologies Corporation</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>ZBRA</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>63.5</v>
+        <v>60.8</v>
       </c>
       <c r="D26" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -2329,28 +2327,28 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0.1005582390165327</v>
+        <v>-0.02271104500520582</v>
       </c>
       <c r="G26" t="n">
-        <v>0.2014836612049711</v>
+        <v>-0.02405904398946013</v>
       </c>
       <c r="H26" t="n">
-        <v>0.50469</v>
+        <v>0.49581</v>
       </c>
       <c r="I26" t="n">
-        <v>0.22840999</v>
+        <v>0.07315000000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>0.1826586942675159</v>
+        <v>0.1582737270304391</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.7002866242038217</v>
+        <v>-0.4415766587179127</v>
       </c>
       <c r="L26" t="n">
-        <v>0.2608341898221838</v>
+        <v>0.3584286531130877</v>
       </c>
       <c r="M26" t="n">
-        <v>392914796544</v>
+        <v>16863885312</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -2359,7 +2357,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
+          <t>Høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P26" t="n">
@@ -2369,33 +2367,33 @@
         <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>0.03964138812961071</v>
+        <v>0.4630792803147783</v>
       </c>
       <c r="S26" t="n">
-        <v>0.2844915016830847</v>
+        <v>0.5915788601597702</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-08-23 07:36:41</t>
+          <t>2026-08-30 12:41:47</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Axon Enterprise, Inc.</t>
+          <t>VeriSign, Inc.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>AXON</t>
+          <t>VRSN</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>63.4</v>
+        <v>60.8</v>
       </c>
       <c r="D27" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -2403,37 +2401,37 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>0.3278726393918761</v>
+        <v>0.05150438997980311</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.09393302099393697</v>
+        <v>0.1218387563505456</v>
       </c>
       <c r="H27" t="n">
-        <v>0.5952499999999999</v>
+        <v>0.88465</v>
       </c>
       <c r="I27" t="n">
-        <v>0.00509</v>
+        <v>0.45124</v>
       </c>
       <c r="J27" t="n">
-        <v>0.104586602947033</v>
+        <v>0.08930222998664061</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.4599601752289925</v>
+        <v>-0.2845545164936799</v>
       </c>
       <c r="L27" t="n">
-        <v>0.2273818660386506</v>
+        <v>0.3138317081979054</v>
       </c>
       <c r="M27" t="n">
-        <v>50996789248</v>
+        <v>26390470656</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P27" t="n">
@@ -2443,33 +2441,33 @@
         <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>0.6102760257977811</v>
+        <v>0.02595474176693791</v>
       </c>
       <c r="S27" t="n">
-        <v>0.4467285720585414</v>
+        <v>0.2879082891485421</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-08-23 07:36:41</t>
+          <t>2026-08-30 12:41:47</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>F5, Inc.</t>
+          <t>Hewlett Packard Enterprise Comp</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>HPE</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>63.3</v>
+        <v>60.7</v>
       </c>
       <c r="D28" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -2477,28 +2475,26 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>0.04631913174341684</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.3082491584064506</v>
-      </c>
+        <v>0.06370170685761956</v>
+      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
-        <v>0.81865996</v>
+        <v>0.33776</v>
       </c>
       <c r="I28" t="n">
-        <v>0.07976999999999999</v>
+        <v>0.01966</v>
       </c>
       <c r="J28" t="n">
-        <v>0.1338169149572317</v>
+        <v>0.2492227107627605</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.4182461066479474</v>
+        <v>-0.6207226151787422</v>
       </c>
       <c r="L28" t="n">
-        <v>0.3199477839249085</v>
+        <v>0.401504157684016</v>
       </c>
       <c r="M28" t="n">
-        <v>21780514816</v>
+        <v>69269086208</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2507,43 +2503,43 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
+          <t>Positivt momentum, analytiker-upside over 20 %</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="Q28" t="b">
         <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>0.002423749403686282</v>
+        <v>0.2189368400139915</v>
       </c>
       <c r="S28" t="n">
-        <v>0.381622847962199</v>
+        <v>1.459307484343893</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-08-23 07:36:41</t>
+          <t>2026-08-30 12:41:47</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise Comp</t>
+          <t>Palo Alto Networks, Inc.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>HPE</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>63.1</v>
+        <v>60.6</v>
       </c>
       <c r="D29" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -2551,26 +2547,26 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>0.06370170685761956</v>
+        <v>0.1878825003317091</v>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
-        <v>0.33776</v>
+        <v>0.71963996</v>
       </c>
       <c r="I29" t="n">
-        <v>0.01966</v>
+        <v>0.017719999</v>
       </c>
       <c r="J29" t="n">
-        <v>0.2206095416276894</v>
+        <v>-0.02038806211146682</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.6288119738072966</v>
+        <v>-0.6243978578540865</v>
       </c>
       <c r="L29" t="n">
-        <v>0.3508354656352276</v>
+        <v>-0.03265235755538296</v>
       </c>
       <c r="M29" t="n">
-        <v>70778675200</v>
+        <v>302845853696</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2579,7 +2575,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Positivt momentum, analytiker-upside over 20 %</t>
+          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P29" t="n">
@@ -2589,33 +2585,33 @@
         <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>0.5780504794710699</v>
+        <v>0.3191451351390586</v>
       </c>
       <c r="S29" t="n">
-        <v>1.524662337871772</v>
+        <v>1.495232345600305</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2026-08-23 07:36:41</t>
+          <t>2026-08-30 12:41:47</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CrowdStrike Holdings, Inc.</t>
+          <t>Corpay, Inc.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>62.6</v>
+        <v>60.2</v>
       </c>
       <c r="D30" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -2623,26 +2619,28 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>0.2900686653697968</v>
-      </c>
-      <c r="G30" t="inlineStr"/>
+        <v>0.097332408585459</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.06564477917470324</v>
+      </c>
       <c r="H30" t="n">
-        <v>0.75136</v>
+        <v>0.8053900000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.0100300005</v>
+        <v>0.06315999999999999</v>
       </c>
       <c r="J30" t="n">
-        <v>0.09265433706694459</v>
+        <v>0.1144734725899774</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.5536337587913518</v>
+        <v>-0.3801117975875258</v>
       </c>
       <c r="L30" t="n">
-        <v>0.1673567328502872</v>
+        <v>0.30115737874097</v>
       </c>
       <c r="M30" t="n">
-        <v>195454861312</v>
+        <v>26781237248</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2651,70 +2649,72 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
+          <t>Høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="Q30" t="b">
         <v>1</v>
       </c>
       <c r="R30" t="n">
-        <v>0.1844561512532248</v>
+        <v>0.1273632356124121</v>
       </c>
       <c r="S30" t="n">
-        <v>0.9758105397158472</v>
+        <v>0.2546293362816447</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2026-08-23 07:36:41</t>
+          <t>2026-08-30 12:41:47</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Marvell Technology, Inc.</t>
+          <t>Gen Digital Inc.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>62.4</v>
+        <v>59.9</v>
       </c>
       <c r="D31" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Monitor</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>0.1144958764235571</v>
-      </c>
-      <c r="G31" t="inlineStr"/>
+        <v>0.1465900735417971</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-0.1008848813150681</v>
+      </c>
       <c r="H31" t="n">
-        <v>0.5150299699999999</v>
+        <v>0.7800700699999999</v>
       </c>
       <c r="I31" t="n">
-        <v>0.03808</v>
+        <v>0.084910005</v>
       </c>
       <c r="J31" t="n">
-        <v>0.1134859095511307</v>
+        <v>0.03504190844616373</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.7408032399595005</v>
+        <v>-0.4268214055448097</v>
       </c>
       <c r="L31" t="n">
-        <v>0.1531930523917997</v>
+        <v>0.0820996978851963</v>
       </c>
       <c r="M31" t="n">
-        <v>212753924096</v>
+        <v>18568169472</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2727,20 +2727,20 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="Q31" t="b">
         <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>0.243371246531729</v>
+        <v>0.2080941360902009</v>
       </c>
       <c r="S31" t="n">
-        <v>1.984614243681185</v>
+        <v>0.3878475674756818</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2026-08-23 07:36:41</t>
+          <t>2026-08-30 12:41:47</t>
         </is>
       </c>
     </row>

--- a/data/compounder_radar.xlsx
+++ b/data/compounder_radar.xlsx
@@ -427,7 +427,7 @@
     <col width="23" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="23" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
     <col width="22" customWidth="1" min="12" max="12"/>
     <col width="17" customWidth="1" min="13" max="13"/>
@@ -435,7 +435,7 @@
     <col width="45" customWidth="1" min="15" max="15"/>
     <col width="19" customWidth="1" min="16" max="16"/>
     <col width="18" customWidth="1" min="17" max="17"/>
-    <col width="22" customWidth="1" min="18" max="18"/>
+    <col width="23" customWidth="1" min="18" max="18"/>
     <col width="21" customWidth="1" min="19" max="19"/>
     <col width="21" customWidth="1" min="20" max="20"/>
   </cols>
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>85.59999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="D2" t="n">
         <v>86</v>
@@ -577,16 +577,16 @@
         <v>0.14119</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2376660354181594</v>
+        <v>0.2438645371039323</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.4138601699252739</v>
+        <v>-0.4090205387552895</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5742665100173138</v>
+        <v>0.596215871814282</v>
       </c>
       <c r="M2" t="n">
-        <v>246418096128</v>
+        <v>244400128000</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -605,33 +605,33 @@
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2251834413195413</v>
+        <v>0.25610937585155</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4635206358263109</v>
+        <v>0.4581985075574582</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-08-30 12:41:47</t>
+          <t>2026-09-06 11:35:57</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Booking Holdings Inc. Common St</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>80</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -639,28 +639,28 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.1634869878187224</v>
+        <v>1.000450949944396</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2943673092572356</v>
+        <v>2.04239508347386</v>
       </c>
       <c r="H3" t="n">
-        <v>0.87227994</v>
+        <v>0.74674004</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2038</v>
+        <v>0.53572</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1598502164081117</v>
+        <v>0.4200732766105226</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.2698536205806547</v>
+        <v>-0.2868987671470742</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5923589836006488</v>
+        <v>1.464186412467847</v>
       </c>
       <c r="M3" t="n">
-        <v>154506379264</v>
+        <v>5562502742016</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -679,33 +679,33 @@
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2312425829203129</v>
+        <v>0.123159403974308</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2184486889498227</v>
+        <v>0.2970472917197908</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-08-30 12:41:47</t>
+          <t>2026-09-06 11:35:57</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>Sandisk Corporation</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>78.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -713,54 +713,52 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.000450949944396</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2.04239508347386</v>
-      </c>
+        <v>0.4928519097558826</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.74674004</v>
+        <v>0.71474</v>
       </c>
       <c r="I4" t="n">
-        <v>0.53572</v>
+        <v>0.43910998</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4866420592967131</v>
+        <v>0.221314367816092</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.2458285451620318</v>
+        <v>-0.961</v>
       </c>
       <c r="L4" t="n">
-        <v>1.979599476439789</v>
+        <v>0.2302959082373486</v>
       </c>
       <c r="M4" t="n">
-        <v>5253179637760</v>
+        <v>254769070080</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
+          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="Q4" t="b">
         <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>0.03155986221998819</v>
+        <v>0.1158710591376246</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2292755810438503</v>
+        <v>2.299641483719194</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-08-30 12:41:47</t>
+          <t>2026-09-06 11:35:57</t>
         </is>
       </c>
     </row>
@@ -776,14 +774,14 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>75.59999999999999</v>
+        <v>74.3</v>
       </c>
       <c r="D5" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>High Conviction</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -799,16 +797,16 @@
         <v>0.07583000500000001</v>
       </c>
       <c r="J5" t="n">
-        <v>0.06282868914669848</v>
+        <v>0.06901039659747732</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.4649246449094654</v>
+        <v>-0.4618124977280162</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1351373600746269</v>
+        <v>0.149433800377834</v>
       </c>
       <c r="M5" t="n">
-        <v>44798558208</v>
+        <v>44539502592</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -827,30 +825,30 @@
         <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5870712874465693</v>
+        <v>0.5937083330349822</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5201912575796177</v>
+        <v>0.4071818947670449</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-08-30 12:41:47</t>
+          <t>2026-09-06 11:35:57</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Expedia Group, Inc.</t>
+          <t>Amphenol Corporation</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>EXPE</t>
+          <t>APH</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>73.2</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D6" t="n">
         <v>73</v>
@@ -861,37 +859,37 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.08087962506974211</v>
+        <v>0.2230660589034148</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6534957812135467</v>
+        <v>0.2972340671812952</v>
       </c>
       <c r="H6" t="n">
-        <v>0.90433</v>
+        <v>0.38952</v>
       </c>
       <c r="I6" t="n">
-        <v>0.061079998</v>
+        <v>0.14473</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02971278533268595</v>
+        <v>0.1977175646291374</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.4374089363768819</v>
+        <v>-0.3332326648949021</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06792907702984081</v>
+        <v>0.5933318832698928</v>
       </c>
       <c r="M6" t="n">
-        <v>39540072448</v>
+        <v>204132728832</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, positivt momentum</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -901,30 +899,30 @@
         <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4611582834734427</v>
+        <v>0.1945088969397628</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5361519933949572</v>
+        <v>0.259858263710129</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-08-30 12:41:47</t>
+          <t>2026-09-06 11:35:57</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>Micron Technology, Inc.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>72.2</v>
+        <v>72.5</v>
       </c>
       <c r="D7" t="n">
         <v>72</v>
@@ -935,37 +933,37 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.1612397915820203</v>
+        <v>0.06713489726936261</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2285599828574523</v>
+        <v>-0.006929629272242499</v>
       </c>
       <c r="H7" t="n">
-        <v>0.67944</v>
+        <v>0.7256899999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.14088</v>
+        <v>0.3487</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1089005510875705</v>
+        <v>0.4884182413755791</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.3200007789223609</v>
+        <v>-0.8736953934231106</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3403133937808073</v>
+        <v>0.5590257715128519</v>
       </c>
       <c r="M7" t="n">
-        <v>3813240733696</v>
+        <v>1148129771520</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
+          <t>Høj bruttomargin, positivt momentum, analytiker-upside over 20 %</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -975,30 +973,30 @@
         <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1427166697123534</v>
+        <v>0.1767761689947756</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3128561087687154</v>
+        <v>1.746890376291639</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-08-30 12:41:47</t>
+          <t>2026-09-06 11:35:57</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Mastercard Incorporated</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>71.5</v>
+        <v>72.5</v>
       </c>
       <c r="D8" t="n">
         <v>72</v>
@@ -1009,32 +1007,32 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.1382198495222513</v>
+        <v>0.1612397915820203</v>
       </c>
       <c r="G8" t="n">
-        <v>0.173598959321368</v>
+        <v>0.2285599828574523</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0.67944</v>
       </c>
       <c r="I8" t="n">
-        <v>0.24063</v>
+        <v>0.14088</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1245750041995635</v>
+        <v>0.1465182309385631</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.2196875524945405</v>
+        <v>-0.3011807084250551</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5670553601468126</v>
+        <v>0.486479468438538</v>
       </c>
       <c r="M8" t="n">
-        <v>521488695296</v>
+        <v>3710545297408</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1049,33 +1047,33 @@
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2071296354970109</v>
+        <v>0.2015280836479112</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1548937127565413</v>
+        <v>0.2268315631847659</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-08-30 12:41:47</t>
+          <t>2026-09-06 11:35:57</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Robinhood Markets, Inc.</t>
+          <t>Advanced Micro Devices, Inc.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>70.3</v>
+        <v>71.7</v>
       </c>
       <c r="D9" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1083,26 +1081,28 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.4878747583673768</v>
-      </c>
-      <c r="G9" t="inlineStr"/>
+        <v>0.1364359933536843</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.4666355102918431</v>
+      </c>
       <c r="H9" t="n">
-        <v>0.9189000000000001</v>
+        <v>0.55724</v>
       </c>
       <c r="I9" t="n">
-        <v>0.04528</v>
+        <v>0.05128</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1654074429311336</v>
+        <v>0.2853506292271291</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.3908018415499712</v>
+        <v>-0.6875431873861424</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4232514418947108</v>
+        <v>0.415029389371098</v>
       </c>
       <c r="M9" t="n">
-        <v>93738319872</v>
+        <v>779621105664</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -1111,43 +1111,43 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="Q9" t="b">
         <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1056203474246546</v>
+        <v>0.02399331515985126</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3745550986636137</v>
+        <v>1.48178571689113</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-08-30 12:41:47</t>
+          <t>2026-09-06 11:35:57</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Fortinet, Inc.</t>
+          <t>Interactive Brokers Group, Inc.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FTNT</t>
+          <t>IBKR</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>69.2</v>
+        <v>71.3</v>
       </c>
       <c r="D10" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1155,28 +1155,28 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.1546194776009138</v>
+        <v>0.3459787421885367</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3167495145145989</v>
+        <v>0.3328887406583814</v>
       </c>
       <c r="H10" t="n">
-        <v>0.80204004</v>
+        <v>0.93036</v>
       </c>
       <c r="I10" t="n">
-        <v>0.14166</v>
+        <v>0.022839999</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.03093463855421696</v>
+        <v>0.1416374433167782</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5569277108433734</v>
+        <v>-0.3635283955949039</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.05554515954570056</v>
+        <v>0.3896186516186515</v>
       </c>
       <c r="M10" t="n">
-        <v>121796468736</v>
+        <v>157807394816</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1195,33 +1195,33 @@
         <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2031600966246192</v>
+        <v>0.09838686751587034</v>
       </c>
       <c r="S10" t="n">
-        <v>1.100468209085766</v>
+        <v>0.3912707391772128</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-08-30 12:41:47</t>
+          <t>2026-09-06 11:35:57</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Interactive Brokers Group, Inc.</t>
+          <t>Expedia Group, Inc.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IBKR</t>
+          <t>EXPE</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>69.2</v>
+        <v>71.2</v>
       </c>
       <c r="D11" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1229,28 +1229,28 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.3459787421885367</v>
+        <v>0.08087962506974211</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3328887406583814</v>
+        <v>0.6534957812135467</v>
       </c>
       <c r="H11" t="n">
-        <v>0.93036</v>
+        <v>0.90433</v>
       </c>
       <c r="I11" t="n">
-        <v>0.022839999</v>
+        <v>0.061079998</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1074011894824707</v>
+        <v>0.1401341095155011</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.3849123539232053</v>
+        <v>-0.37813716279694</v>
       </c>
       <c r="L11" t="n">
-        <v>0.279027649769585</v>
+        <v>0.3705906832298132</v>
       </c>
       <c r="M11" t="n">
-        <v>163293675520</v>
+        <v>35771379712</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
+          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -1269,33 +1269,33 @@
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1031052710980649</v>
+        <v>0.3040443142797304</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3476200478588702</v>
+        <v>0.1982347273512726</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-08-30 12:41:47</t>
+          <t>2026-09-06 11:35:57</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Salesforce, Inc.</t>
+          <t>Blackstone Inc.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>68.90000000000001</v>
+        <v>70.3</v>
       </c>
       <c r="D12" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1303,37 +1303,37 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.09820006113830493</v>
+        <v>0.2027465724146367</v>
       </c>
       <c r="G12" t="n">
-        <v>2.336504917866317</v>
+        <v>0.1792330812083591</v>
       </c>
       <c r="H12" t="n">
-        <v>0.77282</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>0.05704</v>
+        <v>0.1433</v>
       </c>
       <c r="J12" t="n">
-        <v>0.02555214843750009</v>
+        <v>0.05800675725302962</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.4284375</v>
+        <v>-0.2528094013955197</v>
       </c>
       <c r="L12" t="n">
-        <v>0.05964031728665228</v>
+        <v>0.229448576409064</v>
       </c>
       <c r="M12" t="n">
-        <v>210688000000</v>
+        <v>162739781632</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -1343,33 +1343,33 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3430702605548377</v>
+        <v>0.1923610114439704</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3209232029688069</v>
+        <v>0.2573665935775524</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-08-30 12:41:47</t>
+          <t>2026-09-06 11:35:57</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Blackstone Inc.</t>
+          <t>Palo Alto Networks, Inc.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>67.8</v>
+        <v>70</v>
       </c>
       <c r="D13" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1377,73 +1377,71 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.2027465724146367</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.1792330812083591</v>
-      </c>
+        <v>0.1878825003317091</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0.70488</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1433</v>
+        <v>0.01746</v>
       </c>
       <c r="J13" t="n">
-        <v>0.01164140740220532</v>
+        <v>0.1717577867130768</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.2855537607978087</v>
+        <v>-0.5811978635299766</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0407678307919335</v>
+        <v>0.2955237751045485</v>
       </c>
       <c r="M13" t="n">
-        <v>170198450176</v>
+        <v>271606906880</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
+          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="Q13" t="b">
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0.2297383676281706</v>
+        <v>0.2249954961190344</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2805445058422442</v>
+        <v>1.019145735254052</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-08-30 12:41:47</t>
+          <t>2026-09-06 11:35:57</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Incyte Corporation</t>
+          <t>Mastercard Incorporated</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>INCY</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>67.59999999999999</v>
+        <v>69.7</v>
       </c>
       <c r="D14" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1451,32 +1449,32 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.1483959547833886</v>
+        <v>0.1382198495222513</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6156160063417289</v>
+        <v>0.173598959321368</v>
       </c>
       <c r="H14" t="n">
-        <v>0.55659</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>0.16832</v>
+        <v>0.24063</v>
       </c>
       <c r="J14" t="n">
-        <v>0.02215164428720739</v>
+        <v>0.1583345418760034</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.3479938892015759</v>
+        <v>-0.1980110840627752</v>
       </c>
       <c r="L14" t="n">
-        <v>0.06365526802218077</v>
+        <v>0.7996246403348145</v>
       </c>
       <c r="M14" t="n">
-        <v>25209518080</v>
+        <v>507393736704</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1491,33 +1489,33 @@
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0.2856109726374132</v>
+        <v>0.1814388483028617</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2281031585784812</v>
+        <v>0.1126430407173609</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-08-30 12:41:47</t>
+          <t>2026-09-06 11:35:57</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Visa Inc.</t>
+          <t>Salesforce, Inc.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>67.59999999999999</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1525,37 +1523,37 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0.1092124213025429</v>
+        <v>0.09820006113830493</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1337066930484769</v>
+        <v>2.336504917866317</v>
       </c>
       <c r="H15" t="n">
-        <v>0.97725</v>
+        <v>0.77282</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1911</v>
+        <v>0.05704</v>
       </c>
       <c r="J15" t="n">
-        <v>0.09513144654088035</v>
+        <v>0.0447715156424795</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.2298480083857443</v>
+        <v>-0.4355591559618872</v>
       </c>
       <c r="L15" t="n">
-        <v>0.4138884961805944</v>
+        <v>0.1027908954034183</v>
       </c>
       <c r="M15" t="n">
-        <v>712465252352</v>
+        <v>213346304000</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
+          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -1565,14 +1563,14 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0.171433177938783</v>
+        <v>0.3998657393060088</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1966684830677541</v>
+        <v>0.2891448931981548</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-08-30 12:41:47</t>
+          <t>2026-09-06 11:35:57</t>
         </is>
       </c>
     </row>
@@ -1588,10 +1586,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>67.5</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="D16" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1611,16 +1609,16 @@
         <v>0.103310004</v>
       </c>
       <c r="J16" t="n">
-        <v>0.03633560889671883</v>
+        <v>0.07076222980659841</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.4042061219995595</v>
+        <v>-0.3844141069397042</v>
       </c>
       <c r="L16" t="n">
-        <v>0.08989376191773371</v>
+        <v>0.1840781296241492</v>
       </c>
       <c r="M16" t="n">
-        <v>34271905792</v>
+        <v>33170012160</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1639,33 +1637,33 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2316246586094162</v>
+        <v>0.2064232883548802</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2368241770036148</v>
+        <v>0.2907489500059546</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-08-30 12:41:47</t>
+          <t>2026-09-06 11:35:57</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc.</t>
+          <t>Seagate Technology Holdings PLC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>STX</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>67.40000000000001</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1673,26 +1671,26 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0.3291712528765784</v>
+        <v>0.1820341908356484</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>0.84796</v>
+        <v>0.45576</v>
       </c>
       <c r="I17" t="n">
-        <v>0.17292999</v>
+        <v>0.29354998</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0289333834344303</v>
+        <v>0.3246514694800302</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.4290085350797144</v>
+        <v>-0.7796015448379804</v>
       </c>
       <c r="L17" t="n">
-        <v>0.06744244244244271</v>
+        <v>0.4164325630569402</v>
       </c>
       <c r="M17" t="n">
-        <v>447665733632</v>
+        <v>192484655104</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1711,33 +1709,33 @@
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0.1900472804136464</v>
+        <v>0.002850367079626048</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3578977328591939</v>
+        <v>1.413175079577211</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-08-30 12:41:47</t>
+          <t>2026-09-06 11:35:57</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>News Corporation</t>
+          <t>Lam Research Corporation</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NWSA</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>66.59999999999999</v>
+        <v>68.3</v>
       </c>
       <c r="D18" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1745,37 +1743,37 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0.0405993172034298</v>
+        <v>0.1005582390165327</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5822968332827563</v>
+        <v>0.2014836612049711</v>
       </c>
       <c r="H18" t="n">
-        <v>0.57167</v>
+        <v>0.50469</v>
       </c>
       <c r="I18" t="n">
-        <v>0.04658</v>
+        <v>0.22840999</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1676622537939942</v>
+        <v>0.2054964082561352</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.2831772683241847</v>
+        <v>-0.6604583130180399</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5920752565564427</v>
+        <v>0.3111421329789852</v>
       </c>
       <c r="M18" t="n">
-        <v>16635842560</v>
+        <v>384968884224</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -1785,33 +1783,33 @@
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>0.1865899946630778</v>
+        <v>0.01512373068940587</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2803382915574564</v>
+        <v>0.5445076813061343</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-08-30 12:41:47</t>
+          <t>2026-09-06 11:35:57</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DoorDash, Inc.</t>
+          <t>Robinhood Markets, Inc.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DASH</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>65.09999999999999</v>
+        <v>68</v>
       </c>
       <c r="D19" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1819,26 +1817,26 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0.2772574009717286</v>
+        <v>0.4878747583673768</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>0.52225</v>
+        <v>0.9189000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>0.029719999</v>
+        <v>0.04528</v>
       </c>
       <c r="J19" t="n">
-        <v>0.06571605981245243</v>
+        <v>0.01036409794447635</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.3946946016727211</v>
+        <v>-0.4798542297928098</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1664985017123287</v>
+        <v>0.02159842990016224</v>
       </c>
       <c r="M19" t="n">
-        <v>102578962432</v>
+        <v>109786939392</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1857,33 +1855,33 @@
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4862201988288599</v>
+        <v>0.4806596192907207</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3415311602853335</v>
+        <v>0.5839928189273125</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-08-30 12:41:47</t>
+          <t>2026-09-06 11:35:57</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>F5, Inc.</t>
+          <t>Fortinet, Inc.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>FTNT</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>63.5</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="D20" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1891,28 +1889,28 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0.04631913174341684</v>
+        <v>0.1546194776009138</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3082491584064506</v>
+        <v>0.3167495145145989</v>
       </c>
       <c r="H20" t="n">
-        <v>0.81865996</v>
+        <v>0.80204004</v>
       </c>
       <c r="I20" t="n">
-        <v>0.07976999999999999</v>
+        <v>0.14166</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1061789772727273</v>
+        <v>0.0384008573805108</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.432426948051948</v>
+        <v>-0.5294004734787894</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2455419990614735</v>
+        <v>0.07253649987913988</v>
       </c>
       <c r="M20" t="n">
-        <v>22324701184</v>
+        <v>114672107520</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -1921,7 +1919,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P20" t="n">
@@ -1931,33 +1929,33 @@
         <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>0.0281392037654129</v>
+        <v>0.08024606855191685</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4528302311175849</v>
+        <v>0.8679335091002895</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-08-30 12:41:47</t>
+          <t>2026-09-06 11:35:57</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Marvell Technology, Inc.</t>
+          <t>Incyte Corporation</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>INCY</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>63.5</v>
+        <v>67.8</v>
       </c>
       <c r="D21" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1965,26 +1963,28 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0.1144958764235571</v>
-      </c>
-      <c r="G21" t="inlineStr"/>
+        <v>0.1483959547833886</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.6156160063417289</v>
+      </c>
       <c r="H21" t="n">
-        <v>0.52216</v>
+        <v>0.55659</v>
       </c>
       <c r="I21" t="n">
-        <v>0.04125</v>
+        <v>0.16832</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2874706859939065</v>
+        <v>0.002958579881656709</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.7163696796233034</v>
+        <v>-0.3602366863905325</v>
       </c>
       <c r="L21" t="n">
-        <v>0.401288181466684</v>
+        <v>0.008212877792378184</v>
       </c>
       <c r="M21" t="n">
-        <v>194677391360</v>
+        <v>25691938816</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -1993,43 +1993,43 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="Q21" t="b">
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0.05694362072151526</v>
+        <v>0.2380348056296557</v>
       </c>
       <c r="S21" t="n">
-        <v>1.653714013332679</v>
+        <v>0.3211381777628204</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-08-30 12:41:47</t>
+          <t>2026-09-06 11:35:57</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Workday, Inc.</t>
+          <t>Visa Inc.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>63.3</v>
+        <v>67.5</v>
       </c>
       <c r="D22" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -2037,71 +2037,73 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0.1539697807235301</v>
-      </c>
-      <c r="G22" t="inlineStr"/>
+        <v>0.1092124213025429</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.1337066930484769</v>
+      </c>
       <c r="H22" t="n">
-        <v>0.75795</v>
+        <v>0.97725</v>
       </c>
       <c r="I22" t="n">
-        <v>0.04513</v>
+        <v>0.1911</v>
       </c>
       <c r="J22" t="n">
-        <v>0.003669939429464586</v>
+        <v>0.1180889700589223</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.4609222352481438</v>
+        <v>-0.2164395979417175</v>
       </c>
       <c r="L22" t="n">
-        <v>0.007962166172106719</v>
+        <v>0.5455978073417096</v>
       </c>
       <c r="M22" t="n">
-        <v>49337520128</v>
+        <v>700273459200</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="Q22" t="b">
         <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>0.4003693672743183</v>
+        <v>0.1613153107304006</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5305024643241945</v>
+        <v>0.1864941770015818</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-08-30 12:41:47</t>
+          <t>2026-09-06 11:35:57</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>KKR &amp; Co. Inc.</t>
+          <t>CrowdStrike Holdings, Inc.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>KKR</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>62.3</v>
+        <v>66.7</v>
       </c>
       <c r="D23" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -2109,30 +2111,30 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0.5112422937117458</v>
+        <v>0.2900686653697968</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>0.54767</v>
+        <v>0.75185996</v>
       </c>
       <c r="I23" t="n">
-        <v>0.01386</v>
+        <v>-0.0078100003</v>
       </c>
       <c r="J23" t="n">
-        <v>0.1775487670224511</v>
+        <v>0.08653214453308311</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.2393264630106736</v>
+        <v>-0.5979352416705772</v>
       </c>
       <c r="L23" t="n">
-        <v>0.741868512110726</v>
+        <v>0.1447182545911161</v>
       </c>
       <c r="M23" t="n">
-        <v>100375822336</v>
+        <v>218200522752</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2147,33 +2149,33 @@
         <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>0.1349439420001135</v>
+        <v>0.2703049083535807</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2442996153695307</v>
+        <v>0.9869928059355442</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-08-30 12:41:47</t>
+          <t>2026-09-06 11:35:57</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ServiceNow, Inc.</t>
+          <t>Palantir Technologies Inc.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NOW</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>61.7</v>
+        <v>66.7</v>
       </c>
       <c r="D24" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -2181,28 +2183,26 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0.2237651786474262</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.7345580184539504</v>
-      </c>
+        <v>0.3291712528765784</v>
+      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>0.74768996</v>
+        <v>0.84796</v>
       </c>
       <c r="I24" t="n">
-        <v>0.04249</v>
+        <v>0.17292999</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.01712569967521249</v>
+        <v>0.09952389147020013</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.4386013406122591</v>
+        <v>-0.3898353697011415</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.03904616354183077</v>
+        <v>0.2552972336668627</v>
       </c>
       <c r="M24" t="n">
-        <v>149610184704</v>
+        <v>418925182976</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -2211,43 +2211,43 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
+          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="Q24" t="b">
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0.1635442913733003</v>
+        <v>0.2862835047681325</v>
       </c>
       <c r="S24" t="n">
-        <v>0.3397833890545421</v>
+        <v>0.1092517037977452</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-08-30 12:41:47</t>
+          <t>2026-09-06 11:35:57</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CrowdStrike Holdings, Inc.</t>
+          <t>DoorDash, Inc.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>DASH</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>61</v>
+        <v>65.7</v>
       </c>
       <c r="D25" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -2255,30 +2255,30 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0.2900686653697968</v>
+        <v>0.2772574009717286</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>0.75185996</v>
+        <v>0.52225</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.0078100003</v>
+        <v>0.029719999</v>
       </c>
       <c r="J25" t="n">
-        <v>0.04204043040293026</v>
+        <v>0.1988538704954423</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.6076923076923078</v>
+        <v>-0.3231946346762385</v>
       </c>
       <c r="L25" t="n">
-        <v>0.06918045509342954</v>
+        <v>0.6152759023819964</v>
       </c>
       <c r="M25" t="n">
-        <v>223627362304</v>
+        <v>91742175232</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2293,33 +2293,33 @@
         <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0.1950752059999146</v>
+        <v>0.350318824022277</v>
       </c>
       <c r="S25" t="n">
-        <v>1.348513225937955</v>
+        <v>0.1817268398244434</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-08-30 12:41:47</t>
+          <t>2026-09-06 11:35:57</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Zebra Technologies Corporation</t>
+          <t>Corpay, Inc.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ZBRA</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>60.8</v>
+        <v>65.5</v>
       </c>
       <c r="D26" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -2327,28 +2327,28 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>-0.02271104500520582</v>
+        <v>0.097332408585459</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.02405904398946013</v>
+        <v>0.06564477917470324</v>
       </c>
       <c r="H26" t="n">
-        <v>0.49581</v>
+        <v>0.8053900000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>0.07315000000000001</v>
+        <v>0.06315999999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>0.1582737270304391</v>
+        <v>0.1071883180824746</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.4415766587179127</v>
+        <v>-0.392751639167087</v>
       </c>
       <c r="L26" t="n">
-        <v>0.3584286531130877</v>
+        <v>0.2729162844737966</v>
       </c>
       <c r="M26" t="n">
-        <v>16863885312</v>
+        <v>27338686464</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -2367,33 +2367,33 @@
         <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>0.4630792803147783</v>
+        <v>0.1983594200281382</v>
       </c>
       <c r="S26" t="n">
-        <v>0.5915788601597702</v>
+        <v>0.3243320712476749</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-08-30 12:41:47</t>
+          <t>2026-09-06 11:35:57</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>VeriSign, Inc.</t>
+          <t>Dell Technologies Inc.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>VRSN</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>60.8</v>
+        <v>63.7</v>
       </c>
       <c r="D27" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -2401,37 +2401,37 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>0.05150438997980311</v>
+        <v>0.03534983888485344</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1218387563505456</v>
+        <v>0.388859258627138</v>
       </c>
       <c r="H27" t="n">
-        <v>0.88465</v>
+        <v>0.19893</v>
       </c>
       <c r="I27" t="n">
-        <v>0.45124</v>
+        <v>0.08554</v>
       </c>
       <c r="J27" t="n">
-        <v>0.08930222998664061</v>
+        <v>0.07692276872591286</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.2845545164936799</v>
+        <v>-0.7897126721868203</v>
       </c>
       <c r="L27" t="n">
-        <v>0.3138317081979054</v>
+        <v>0.09740602048705056</v>
       </c>
       <c r="M27" t="n">
-        <v>26390470656</v>
+        <v>338669076480</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk eps-vækst, positivt momentum</t>
         </is>
       </c>
       <c r="P27" t="n">
@@ -2441,33 +2441,33 @@
         <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>0.02595474176693791</v>
+        <v>0.3311851479129055</v>
       </c>
       <c r="S27" t="n">
-        <v>0.2879082891485421</v>
+        <v>2.595238758114921</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-08-30 12:41:47</t>
+          <t>2026-09-06 11:35:57</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise Comp</t>
+          <t>Workday, Inc.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>HPE</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>60.7</v>
+        <v>63.7</v>
       </c>
       <c r="D28" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -2475,26 +2475,26 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>0.06370170685761956</v>
+        <v>0.1539697807235301</v>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
-        <v>0.33776</v>
+        <v>0.75795</v>
       </c>
       <c r="I28" t="n">
-        <v>0.01966</v>
+        <v>0.04513</v>
       </c>
       <c r="J28" t="n">
-        <v>0.2492227107627605</v>
+        <v>0.05778073446039134</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.6207226151787422</v>
+        <v>-0.436334848562235</v>
       </c>
       <c r="L28" t="n">
-        <v>0.401504157684016</v>
+        <v>0.132422919349175</v>
       </c>
       <c r="M28" t="n">
-        <v>69269086208</v>
+        <v>47185387520</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Positivt momentum, analytiker-upside over 20 %</t>
+          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P28" t="n">
@@ -2513,33 +2513,33 @@
         <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>0.2189368400139915</v>
+        <v>0.3570141041214594</v>
       </c>
       <c r="S28" t="n">
-        <v>1.459307484343893</v>
+        <v>0.2962791445258133</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-08-30 12:41:47</t>
+          <t>2026-09-06 11:35:57</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Palo Alto Networks, Inc.</t>
+          <t>Lumentum Holdings Inc.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>60.6</v>
+        <v>63.6</v>
       </c>
       <c r="D29" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -2547,26 +2547,26 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>0.1878825003317091</v>
+        <v>0.1948193100306586</v>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
-        <v>0.71963996</v>
+        <v>0.44244</v>
       </c>
       <c r="I29" t="n">
-        <v>0.017719999</v>
+        <v>0.05815</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.02038806211146682</v>
+        <v>0.3031795564280488</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.6243978578540865</v>
+        <v>-0.8360066042178484</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.03265235755538296</v>
+        <v>0.3626521069312577</v>
       </c>
       <c r="M29" t="n">
-        <v>302845853696</v>
+        <v>79048572928</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2585,33 +2585,33 @@
         <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>0.3191451351390586</v>
+        <v>0.02037263771090236</v>
       </c>
       <c r="S29" t="n">
-        <v>1.495232345600305</v>
+        <v>0.5780656848186252</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2026-08-30 12:41:47</t>
+          <t>2026-09-06 11:35:57</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Corpay, Inc.</t>
+          <t>News Corporation</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CPAY</t>
+          <t>NWSA</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>60.2</v>
+        <v>61.9</v>
       </c>
       <c r="D30" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -2619,37 +2619,37 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>0.097332408585459</v>
+        <v>0.0405993172034298</v>
       </c>
       <c r="G30" t="n">
-        <v>0.06564477917470324</v>
+        <v>0.5822968332827563</v>
       </c>
       <c r="H30" t="n">
-        <v>0.8053900000000001</v>
+        <v>0.57167</v>
       </c>
       <c r="I30" t="n">
-        <v>0.06315999999999999</v>
+        <v>0.04658</v>
       </c>
       <c r="J30" t="n">
-        <v>0.1144734725899774</v>
+        <v>0.1899473511023364</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.3801117975875258</v>
+        <v>-0.2694965449160909</v>
       </c>
       <c r="L30" t="n">
-        <v>0.30115737874097</v>
+        <v>0.7048229548229551</v>
       </c>
       <c r="M30" t="n">
-        <v>26781237248</v>
+        <v>16310325248</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Høj bruttomargin, positivt momentum</t>
+          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P30" t="n">
@@ -2659,14 +2659,14 @@
         <v>1</v>
       </c>
       <c r="R30" t="n">
-        <v>0.1273632356124121</v>
+        <v>0.1148202176994255</v>
       </c>
       <c r="S30" t="n">
-        <v>0.2546293362816447</v>
+        <v>0.239520454510977</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2026-08-30 12:41:47</t>
+          <t>2026-09-06 11:35:57</t>
         </is>
       </c>
     </row>
@@ -2682,14 +2682,14 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>59.9</v>
+        <v>60.9</v>
       </c>
       <c r="D31" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Monitor</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -2705,16 +2705,16 @@
         <v>0.084910005</v>
       </c>
       <c r="J31" t="n">
-        <v>0.03504190844616373</v>
+        <v>0.07667210440456773</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.4268214055448097</v>
+        <v>-0.4199021207177813</v>
       </c>
       <c r="L31" t="n">
-        <v>0.0820996978851963</v>
+        <v>0.1825951825951827</v>
       </c>
       <c r="M31" t="n">
-        <v>18568169472</v>
+        <v>18346690560</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2733,14 +2733,14 @@
         <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>0.2080941360902009</v>
+        <v>0.1714275925138224</v>
       </c>
       <c r="S31" t="n">
-        <v>0.3878475674756818</v>
+        <v>0.3688674871134887</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2026-08-30 12:41:47</t>
+          <t>2026-09-06 11:35:57</t>
         </is>
       </c>
     </row>
